--- a/0_documents/2_docs/indiv_model_results_20250529.xlsx
+++ b/0_documents/2_docs/indiv_model_results_20250529.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrew/Documents/04_git/code-generation/0_documents/2_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661729AD-0CB3-774F-96EE-6D625C9B94B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63D4463-4D3C-7D4C-B4AD-C049606E955C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="1840" windowWidth="28960" windowHeight="15380" activeTab="10" xr2:uid="{C9D0F527-0BC8-1244-93BD-714AFEC4ED61}"/>
+    <workbookView xWindow="2060" yWindow="820" windowWidth="27800" windowHeight="14920" firstSheet="7" activeTab="7" xr2:uid="{C9D0F527-0BC8-1244-93BD-714AFEC4ED61}"/>
   </bookViews>
   <sheets>
     <sheet name="HumanEval" sheetId="3" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="LBPP" sheetId="5" r:id="rId3"/>
     <sheet name="MBPP" sheetId="7" r:id="rId4"/>
     <sheet name="HumanEval_Reflection" sheetId="14" r:id="rId5"/>
-    <sheet name="MBPP_Reflection" sheetId="11" r:id="rId6"/>
-    <sheet name="BigCode_Reflection" sheetId="13" r:id="rId7"/>
+    <sheet name="BigCode_Reflection" sheetId="13" r:id="rId6"/>
+    <sheet name="MBPP_Reflection" sheetId="11" r:id="rId7"/>
     <sheet name="LBPP_Reflection" sheetId="10" r:id="rId8"/>
     <sheet name="LBPP_Temp05" sheetId="15" r:id="rId9"/>
     <sheet name="LBPP_Temp025" sheetId="16" r:id="rId10"/>
@@ -530,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -617,7 +617,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -629,71 +629,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -710,6 +665,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1046,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71123669-A44E-B04D-8F8D-7D846D765509}">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -1069,7 +1027,7 @@
     <col min="21" max="21" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1134,784 +1092,850 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="55">
-        <v>1</v>
-      </c>
-      <c r="B2" s="56" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" s="36">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="58">
-        <v>1</v>
-      </c>
-      <c r="F2" s="59">
-        <v>1</v>
-      </c>
-      <c r="G2" s="60">
+      <c r="E2" s="8">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1</v>
+      </c>
+      <c r="G2" s="55">
         <v>0.5</v>
       </c>
-      <c r="H2" s="61">
+      <c r="H2" s="56">
         <v>0.5</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="57">
         <v>5.4878048780487798E-2</v>
       </c>
-      <c r="J2" s="61">
-        <v>0</v>
-      </c>
-      <c r="K2" s="62">
-        <v>0</v>
-      </c>
-      <c r="L2" s="61">
+      <c r="J2" s="56">
+        <v>0</v>
+      </c>
+      <c r="K2" s="57">
+        <v>0</v>
+      </c>
+      <c r="L2" s="56">
         <v>0.77439024390243905</v>
       </c>
-      <c r="M2" s="62">
+      <c r="M2" s="57">
         <v>0.74390243902439002</v>
       </c>
-      <c r="N2" s="61">
+      <c r="N2" s="56">
         <v>0.75</v>
       </c>
-      <c r="O2" s="62">
-        <v>0</v>
-      </c>
-      <c r="P2" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="62">
-        <v>0</v>
-      </c>
-      <c r="R2" s="61">
-        <v>0</v>
-      </c>
-      <c r="S2" s="62">
-        <v>0</v>
-      </c>
-      <c r="T2" s="61">
+      <c r="O2" s="57">
+        <v>0</v>
+      </c>
+      <c r="P2" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="57">
+        <v>0</v>
+      </c>
+      <c r="R2" s="56">
+        <v>0</v>
+      </c>
+      <c r="S2" s="57">
+        <v>0</v>
+      </c>
+      <c r="T2" s="56">
         <v>0.48780487804877998</v>
       </c>
-      <c r="U2" s="63">
+      <c r="U2" s="58">
         <v>0.439024390243902</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="64">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" s="37">
         <v>2</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="67">
-        <v>1</v>
-      </c>
-      <c r="F3" s="68">
-        <v>1</v>
-      </c>
-      <c r="G3" s="69">
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="60">
         <v>0.5</v>
       </c>
-      <c r="H3" s="70">
+      <c r="H3" s="61">
         <v>0.5</v>
       </c>
-      <c r="I3" s="71">
+      <c r="I3" s="4">
         <v>0.45121951219512102</v>
       </c>
-      <c r="J3" s="70">
+      <c r="J3" s="61">
         <v>0.70121951219512102</v>
       </c>
-      <c r="K3" s="71">
+      <c r="K3" s="4">
         <v>0.60975609756097504</v>
       </c>
-      <c r="L3" s="70">
+      <c r="L3" s="61">
         <v>0.78658536585365801</v>
       </c>
-      <c r="M3" s="71">
+      <c r="M3" s="4">
         <v>0.76219512195121897</v>
       </c>
-      <c r="N3" s="70">
+      <c r="N3" s="61">
         <v>0.75609756097560898</v>
       </c>
-      <c r="O3" s="71">
+      <c r="O3" s="4">
         <v>0.81707317073170704</v>
       </c>
-      <c r="P3" s="70">
+      <c r="P3" s="61">
         <v>0.82317073170731703</v>
       </c>
-      <c r="Q3" s="71">
+      <c r="Q3" s="4">
         <v>0.42073170731707299</v>
       </c>
-      <c r="R3" s="70">
+      <c r="R3" s="61">
         <v>0.77439024390243905</v>
       </c>
-      <c r="S3" s="71">
+      <c r="S3" s="4">
         <v>0.792682926829268</v>
       </c>
-      <c r="T3" s="70">
+      <c r="T3" s="61">
         <v>0.68902439024390205</v>
       </c>
-      <c r="U3" s="72">
+      <c r="U3" s="62">
         <v>0.73780487804878003</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64">
+    <row r="4" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="37">
         <v>3</v>
       </c>
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="73">
-        <v>1</v>
-      </c>
-      <c r="F4" s="74">
-        <v>1</v>
-      </c>
-      <c r="G4" s="75">
+      <c r="E4" s="14">
+        <v>1</v>
+      </c>
+      <c r="F4" s="15">
+        <v>1</v>
+      </c>
+      <c r="G4" s="63">
         <v>0.51219512195121897</v>
       </c>
-      <c r="H4" s="76">
+      <c r="H4" s="64">
         <v>0.51219512195121897</v>
       </c>
-      <c r="I4" s="77">
+      <c r="I4" s="65">
         <v>0.45121951219512102</v>
       </c>
-      <c r="J4" s="76">
+      <c r="J4" s="64">
         <v>0.707317073170731</v>
       </c>
-      <c r="K4" s="77">
+      <c r="K4" s="65">
         <v>0.60975609756097504</v>
       </c>
-      <c r="L4" s="76">
+      <c r="L4" s="64">
         <v>0.78048780487804803</v>
       </c>
-      <c r="M4" s="77">
+      <c r="M4" s="65">
         <v>0.76219512195121897</v>
       </c>
-      <c r="N4" s="76">
+      <c r="N4" s="64">
         <v>0.75</v>
       </c>
-      <c r="O4" s="77">
+      <c r="O4" s="65">
         <v>0.82317073170731703</v>
       </c>
-      <c r="P4" s="76">
+      <c r="P4" s="64">
         <v>0.82926829268292601</v>
       </c>
-      <c r="Q4" s="77">
+      <c r="Q4" s="65">
         <v>0.42073170731707299</v>
       </c>
-      <c r="R4" s="76">
+      <c r="R4" s="64">
         <v>0.76829268292682895</v>
       </c>
-      <c r="S4" s="77">
+      <c r="S4" s="65">
         <v>0.78658536585365801</v>
       </c>
-      <c r="T4" s="76">
+      <c r="T4" s="64">
         <v>0.68292682926829196</v>
       </c>
-      <c r="U4" s="78">
+      <c r="U4" s="66">
         <v>0.76219512195121897</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79">
+    <row r="5" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="46">
         <v>4</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="73">
-        <v>1</v>
-      </c>
-      <c r="F5" s="74">
-        <v>1</v>
-      </c>
-      <c r="G5" s="69">
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
+      <c r="F5" s="15">
+        <v>1</v>
+      </c>
+      <c r="G5" s="60">
         <v>0.50609756097560898</v>
       </c>
-      <c r="H5" s="70">
+      <c r="H5" s="61">
         <v>0.50609756097560898</v>
       </c>
-      <c r="I5" s="71">
+      <c r="I5" s="4">
         <v>0.45121951219512102</v>
       </c>
-      <c r="J5" s="70">
+      <c r="J5" s="61">
         <v>0.70121951219512102</v>
       </c>
-      <c r="K5" s="71">
+      <c r="K5" s="4">
         <v>0.60975609756097504</v>
       </c>
-      <c r="L5" s="70">
+      <c r="L5" s="61">
         <v>0.78658536585365801</v>
       </c>
-      <c r="M5" s="71">
+      <c r="M5" s="4">
         <v>0.76219512195121897</v>
       </c>
-      <c r="N5" s="70">
+      <c r="N5" s="61">
         <v>0.75609756097560898</v>
       </c>
-      <c r="O5" s="71">
+      <c r="O5" s="4">
         <v>0.81707317073170704</v>
       </c>
-      <c r="P5" s="70">
+      <c r="P5" s="61">
         <v>0.82317073170731703</v>
       </c>
-      <c r="Q5" s="71">
+      <c r="Q5" s="4">
         <v>0.42073170731707299</v>
       </c>
-      <c r="R5" s="70">
+      <c r="R5" s="61">
         <v>0.77439024390243905</v>
       </c>
-      <c r="S5" s="71">
+      <c r="S5" s="4">
         <v>0.792682926829268</v>
       </c>
-      <c r="T5" s="70">
+      <c r="T5" s="61">
         <v>0.68902439024390205</v>
       </c>
-      <c r="U5" s="72">
+      <c r="U5" s="62">
         <v>0.76219512195121897</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="64">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="37">
         <v>5</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="57" t="s">
+      <c r="C6" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="58">
-        <v>1</v>
-      </c>
-      <c r="F6" s="59">
-        <v>1</v>
-      </c>
-      <c r="G6" s="60">
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9">
+        <v>1</v>
+      </c>
+      <c r="G6" s="55">
         <v>2.4390243902439001E-2</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="56">
         <v>2.4390243902439001E-2</v>
       </c>
-      <c r="I6" s="62">
-        <v>0</v>
-      </c>
-      <c r="J6" s="61">
-        <v>0</v>
-      </c>
-      <c r="K6" s="62">
-        <v>0</v>
-      </c>
-      <c r="L6" s="61">
+      <c r="I6" s="57">
+        <v>0</v>
+      </c>
+      <c r="J6" s="56">
+        <v>0</v>
+      </c>
+      <c r="K6" s="57">
+        <v>0</v>
+      </c>
+      <c r="L6" s="56">
         <v>2.4390243902439001E-2</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="57">
         <v>6.0975609756097502E-3</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="56">
         <v>0.72560975609756095</v>
       </c>
-      <c r="O6" s="62">
-        <v>0</v>
-      </c>
-      <c r="P6" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="62">
-        <v>0</v>
-      </c>
-      <c r="R6" s="61">
-        <v>0</v>
-      </c>
-      <c r="S6" s="62">
-        <v>0</v>
-      </c>
-      <c r="T6" s="61">
-        <v>0</v>
-      </c>
-      <c r="U6" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="64">
+      <c r="O6" s="57">
+        <v>0</v>
+      </c>
+      <c r="P6" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="57">
+        <v>0</v>
+      </c>
+      <c r="R6" s="56">
+        <v>0</v>
+      </c>
+      <c r="S6" s="57">
+        <v>0</v>
+      </c>
+      <c r="T6" s="56">
+        <v>0</v>
+      </c>
+      <c r="U6" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="37">
         <v>6</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="66" t="s">
+      <c r="C7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="67">
-        <v>1</v>
-      </c>
-      <c r="F7" s="68">
-        <v>1</v>
-      </c>
-      <c r="G7" s="69">
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="60">
         <v>0.46341463414634099</v>
       </c>
-      <c r="H7" s="70">
+      <c r="H7" s="61">
         <v>0.46341463414634099</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="4">
         <v>0.44512195121951198</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="61">
         <v>0.65853658536585302</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="4">
         <v>0.55487804878048697</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="61">
         <v>0.81707317073170704</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="4">
         <v>0.76829268292682895</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="61">
         <v>0.76829268292682895</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="4">
         <v>0.78658536585365801</v>
       </c>
-      <c r="P7" s="70">
+      <c r="P7" s="61">
         <v>0.76829268292682895</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="4">
         <v>0.31707317073170699</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="61">
         <v>9.1463414634146298E-2</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="4">
         <v>0.80487804878048697</v>
       </c>
-      <c r="T7" s="70">
+      <c r="T7" s="61">
         <v>0.69512195121951204</v>
       </c>
-      <c r="U7" s="72">
+      <c r="U7" s="62">
         <v>0.62195121951219501</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="64">
+    <row r="8" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37">
         <v>7</v>
       </c>
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="82" t="s">
+      <c r="C8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="73">
-        <v>1</v>
-      </c>
-      <c r="F8" s="74">
-        <v>1</v>
-      </c>
-      <c r="G8" s="75">
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="15">
+        <v>1</v>
+      </c>
+      <c r="G8" s="63">
         <v>0.55487804878048697</v>
       </c>
-      <c r="H8" s="76">
+      <c r="H8" s="64">
         <v>0.55487804878048697</v>
       </c>
-      <c r="I8" s="77">
+      <c r="I8" s="65">
         <v>0.44512195121951198</v>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="64">
         <v>0.68292682926829196</v>
       </c>
-      <c r="K8" s="77">
+      <c r="K8" s="65">
         <v>0.585365853658536</v>
       </c>
-      <c r="L8" s="76">
+      <c r="L8" s="64">
         <v>0.81097560975609695</v>
       </c>
-      <c r="M8" s="77">
+      <c r="M8" s="65">
         <v>0.76219512195121897</v>
       </c>
-      <c r="N8" s="76">
+      <c r="N8" s="64">
         <v>0.76219512195121897</v>
       </c>
-      <c r="O8" s="77">
+      <c r="O8" s="65">
         <v>0.84146341463414598</v>
       </c>
-      <c r="P8" s="76">
+      <c r="P8" s="64">
         <v>0.82926829268292601</v>
       </c>
-      <c r="Q8" s="77">
+      <c r="Q8" s="65">
         <v>0.35975609756097499</v>
       </c>
-      <c r="R8" s="76">
+      <c r="R8" s="64">
         <v>0.75609756097560898</v>
       </c>
-      <c r="S8" s="77">
+      <c r="S8" s="65">
         <v>0.80487804878048697</v>
       </c>
-      <c r="T8" s="76">
+      <c r="T8" s="64">
         <v>0.68902439024390205</v>
       </c>
-      <c r="U8" s="78">
+      <c r="U8" s="66">
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="79">
+    <row r="9" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="46">
         <v>8</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="66" t="s">
+      <c r="C9" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="73">
-        <v>1</v>
-      </c>
-      <c r="F9" s="74">
-        <v>1</v>
-      </c>
-      <c r="G9" s="69">
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15">
+        <v>1</v>
+      </c>
+      <c r="G9" s="60">
         <v>0.56097560975609695</v>
       </c>
-      <c r="H9" s="70">
+      <c r="H9" s="61">
         <v>0.56097560975609695</v>
       </c>
-      <c r="I9" s="71">
+      <c r="I9" s="4">
         <v>0.44512195121951198</v>
       </c>
-      <c r="J9" s="70">
+      <c r="J9" s="61">
         <v>0.67073170731707299</v>
       </c>
-      <c r="K9" s="71">
+      <c r="K9" s="4">
         <v>0.585365853658536</v>
       </c>
-      <c r="L9" s="70">
+      <c r="L9" s="61">
         <v>0.81707317073170704</v>
       </c>
-      <c r="M9" s="71">
+      <c r="M9" s="4">
         <v>0.76829268292682895</v>
       </c>
-      <c r="N9" s="70">
+      <c r="N9" s="61">
         <v>0.76829268292682895</v>
       </c>
-      <c r="O9" s="71">
+      <c r="O9" s="4">
         <v>0.84146341463414598</v>
       </c>
-      <c r="P9" s="70">
+      <c r="P9" s="61">
         <v>0.82926829268292601</v>
       </c>
-      <c r="Q9" s="71">
+      <c r="Q9" s="4">
         <v>0.35975609756097499</v>
       </c>
-      <c r="R9" s="70">
+      <c r="R9" s="61">
         <v>0.75609756097560898</v>
       </c>
-      <c r="S9" s="71">
+      <c r="S9" s="4">
         <v>0.80487804878048697</v>
       </c>
-      <c r="T9" s="70">
+      <c r="T9" s="61">
         <v>0.69512195121951204</v>
       </c>
-      <c r="U9" s="72">
+      <c r="U9" s="62">
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="55">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" s="36">
         <v>9</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="58">
-        <v>1</v>
-      </c>
-      <c r="F10" s="59">
-        <v>1</v>
-      </c>
-      <c r="G10" s="60">
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9">
+        <v>1</v>
+      </c>
+      <c r="G10" s="55">
         <v>4.8780487804878002E-2</v>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="56">
         <v>4.8780487804878002E-2</v>
       </c>
-      <c r="I10" s="62">
-        <v>0</v>
-      </c>
-      <c r="J10" s="61">
-        <v>0</v>
-      </c>
-      <c r="K10" s="62">
-        <v>0</v>
-      </c>
-      <c r="L10" s="61">
-        <v>0</v>
-      </c>
-      <c r="M10" s="62">
-        <v>0</v>
-      </c>
-      <c r="N10" s="61">
+      <c r="I10" s="57">
+        <v>0</v>
+      </c>
+      <c r="J10" s="56">
+        <v>0</v>
+      </c>
+      <c r="K10" s="57">
+        <v>0</v>
+      </c>
+      <c r="L10" s="56">
+        <v>0</v>
+      </c>
+      <c r="M10" s="57">
+        <v>0</v>
+      </c>
+      <c r="N10" s="56">
         <v>0.60975609756097504</v>
       </c>
-      <c r="O10" s="62">
-        <v>0</v>
-      </c>
-      <c r="P10" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="62">
-        <v>0</v>
-      </c>
-      <c r="R10" s="61">
-        <v>0</v>
-      </c>
-      <c r="S10" s="62">
-        <v>0</v>
-      </c>
-      <c r="T10" s="61">
-        <v>0</v>
-      </c>
-      <c r="U10" s="63">
+      <c r="O10" s="57">
+        <v>0</v>
+      </c>
+      <c r="P10" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="57">
+        <v>0</v>
+      </c>
+      <c r="R10" s="56">
+        <v>0</v>
+      </c>
+      <c r="S10" s="57">
+        <v>0</v>
+      </c>
+      <c r="T10" s="56">
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
         <v>6.0975609756097502E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="64">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="37">
         <v>10</v>
       </c>
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="67">
-        <v>1</v>
-      </c>
-      <c r="F11" s="68">
-        <v>1</v>
-      </c>
-      <c r="G11" s="69">
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="60">
         <v>0.25609756097560898</v>
       </c>
-      <c r="H11" s="70">
+      <c r="H11" s="61">
         <v>0.25609756097560898</v>
       </c>
-      <c r="I11" s="71">
+      <c r="I11" s="4">
         <v>0.34146341463414598</v>
       </c>
-      <c r="J11" s="70">
+      <c r="J11" s="61">
         <v>0.585365853658536</v>
       </c>
-      <c r="K11" s="71">
+      <c r="K11" s="4">
         <v>0.51219512195121897</v>
       </c>
-      <c r="L11" s="70">
+      <c r="L11" s="61">
         <v>0.72560975609756095</v>
       </c>
-      <c r="M11" s="71">
+      <c r="M11" s="4">
         <v>0.71341463414634099</v>
       </c>
-      <c r="N11" s="70">
+      <c r="N11" s="61">
         <v>0.68292682926829196</v>
       </c>
-      <c r="O11" s="71">
+      <c r="O11" s="4">
         <v>0.75609756097560898</v>
       </c>
-      <c r="P11" s="70">
+      <c r="P11" s="61">
         <v>0.75</v>
       </c>
-      <c r="Q11" s="71">
+      <c r="Q11" s="4">
         <v>0.31707317073170699</v>
       </c>
-      <c r="R11" s="70">
+      <c r="R11" s="61">
         <v>0.64024390243902396</v>
       </c>
-      <c r="S11" s="71">
+      <c r="S11" s="4">
         <v>0.73170731707317005</v>
       </c>
-      <c r="T11" s="70">
+      <c r="T11" s="61">
         <v>0.32317073170731703</v>
       </c>
-      <c r="U11" s="72">
+      <c r="U11" s="62">
         <v>0.53048780487804803</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="64">
+    <row r="12" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37">
         <v>11</v>
       </c>
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="82" t="s">
+      <c r="D12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="73">
-        <v>1</v>
-      </c>
-      <c r="F12" s="74">
-        <v>1</v>
-      </c>
-      <c r="G12" s="75">
+      <c r="E12" s="14">
+        <v>1</v>
+      </c>
+      <c r="F12" s="15">
+        <v>1</v>
+      </c>
+      <c r="G12" s="63">
         <v>0.54878048780487798</v>
       </c>
-      <c r="H12" s="76">
+      <c r="H12" s="64">
         <v>0.54878048780487798</v>
       </c>
-      <c r="I12" s="77">
+      <c r="I12" s="65">
         <v>0.41463414634146301</v>
       </c>
-      <c r="J12" s="76">
+      <c r="J12" s="64">
         <v>0.585365853658536</v>
       </c>
-      <c r="K12" s="77">
+      <c r="K12" s="65">
         <v>0.542682926829268</v>
       </c>
-      <c r="L12" s="76">
+      <c r="L12" s="64">
         <v>0.72560975609756095</v>
       </c>
-      <c r="M12" s="77">
+      <c r="M12" s="65">
         <v>0.71951219512195097</v>
       </c>
-      <c r="N12" s="76">
+      <c r="N12" s="64">
         <v>0.69512195121951204</v>
       </c>
-      <c r="O12" s="77">
+      <c r="O12" s="65">
         <v>0.78048780487804803</v>
       </c>
-      <c r="P12" s="76">
+      <c r="P12" s="64">
         <v>0.77439024390243905</v>
       </c>
-      <c r="Q12" s="77">
+      <c r="Q12" s="65">
         <v>0.37195121951219501</v>
       </c>
-      <c r="R12" s="76">
+      <c r="R12" s="64">
         <v>0.71341463414634099</v>
       </c>
-      <c r="S12" s="77">
+      <c r="S12" s="65">
         <v>0.73780487804878003</v>
       </c>
-      <c r="T12" s="76">
+      <c r="T12" s="64">
         <v>0.51829268292682895</v>
       </c>
-      <c r="U12" s="78">
+      <c r="U12" s="66">
         <v>0.73170731707317005</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="79">
+    <row r="13" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="46">
         <v>12</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="82" t="s">
+      <c r="D13" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="73">
-        <v>1</v>
-      </c>
-      <c r="F13" s="74">
-        <v>1</v>
-      </c>
-      <c r="G13" s="83">
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13">
         <v>0.542682926829268</v>
       </c>
-      <c r="H13" s="83">
+      <c r="H13" s="13">
         <v>0.542682926829268</v>
       </c>
-      <c r="I13" s="83">
+      <c r="I13" s="13">
         <v>0.41463414634146301</v>
       </c>
-      <c r="J13" s="83">
+      <c r="J13" s="13">
         <v>0.585365853658536</v>
       </c>
-      <c r="K13" s="83">
+      <c r="K13" s="13">
         <v>0.542682926829268</v>
       </c>
-      <c r="L13" s="83">
+      <c r="L13" s="13">
         <v>0.72560975609756095</v>
       </c>
-      <c r="M13" s="83">
+      <c r="M13" s="13">
         <v>0.71951219512195097</v>
       </c>
-      <c r="N13" s="83">
+      <c r="N13" s="13">
         <v>0.69512195121951204</v>
       </c>
-      <c r="O13" s="83">
+      <c r="O13" s="13">
         <v>0.78048780487804803</v>
       </c>
-      <c r="P13" s="83">
+      <c r="P13" s="13">
         <v>0.77439024390243905</v>
       </c>
-      <c r="Q13" s="83">
+      <c r="Q13" s="13">
         <v>0.37195121951219501</v>
       </c>
-      <c r="R13" s="83">
+      <c r="R13" s="13">
         <v>0.71341463414634099</v>
       </c>
-      <c r="S13" s="83">
+      <c r="S13" s="13">
         <v>0.73780487804878003</v>
       </c>
-      <c r="T13" s="83">
+      <c r="T13" s="13">
         <v>0.51829268292682895</v>
       </c>
-      <c r="U13" s="84">
+      <c r="U13" s="18">
         <v>0.73170731707317005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G14" s="4">
+        <f>MAX(G2:G13)</f>
+        <v>0.56097560975609695</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" ref="H14:U14" si="0">MAX(H2:H13)</f>
+        <v>0.56097560975609695</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.45121951219512102</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.707317073170731</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.60975609756097504</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.81707317073170704</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.76829268292682895</v>
+      </c>
+      <c r="N14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.76829268292682895</v>
+      </c>
+      <c r="O14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.84146341463414598</v>
+      </c>
+      <c r="P14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.82926829268292601</v>
+      </c>
+      <c r="Q14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.42073170731707299</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.77439024390243905</v>
+      </c>
+      <c r="S14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.80487804878048697</v>
+      </c>
+      <c r="T14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.69512195121951204</v>
+      </c>
+      <c r="U14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.76219512195121897</v>
+      </c>
+      <c r="V14" s="76">
+        <f>MAX(G14:U14)</f>
+        <v>0.84146341463414598</v>
       </c>
     </row>
   </sheetData>
@@ -1995,7 +2019,7 @@
       <c r="E2" s="43">
         <v>0.25</v>
       </c>
-      <c r="F2" s="100">
+      <c r="F2" s="73">
         <v>1</v>
       </c>
       <c r="G2" s="7">
@@ -2042,31 +2066,31 @@
       <c r="E3" s="44">
         <v>0.25</v>
       </c>
-      <c r="F3" s="101">
-        <v>1</v>
-      </c>
-      <c r="G3" s="52">
+      <c r="F3" s="74">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>0.172839506172839</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3">
         <v>7.4074074074074001E-2</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.296296296296296</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3">
         <v>0.179012345679012</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3">
         <v>0.25308641975308599</v>
       </c>
-      <c r="L3" s="52">
+      <c r="L3">
         <v>0.25925925925925902</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.29012345679012302</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3">
         <v>0.22839506172839499</v>
       </c>
       <c r="O3" s="20">
@@ -2089,31 +2113,31 @@
       <c r="E4" s="44">
         <v>0.25</v>
       </c>
-      <c r="F4" s="101">
-        <v>1</v>
-      </c>
-      <c r="G4" s="52">
+      <c r="F4" s="74">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>0.15432098765432001</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4">
         <v>0.11111111111111099</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.265432098765432</v>
       </c>
-      <c r="J4" s="52">
+      <c r="J4">
         <v>0.172839506172839</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4">
         <v>0.25308641975308599</v>
       </c>
-      <c r="L4" s="52">
+      <c r="L4">
         <v>0.265432098765432</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.28395061728394999</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4">
         <v>0.22839506172839499</v>
       </c>
       <c r="O4" s="20">
@@ -2136,31 +2160,31 @@
       <c r="E5" s="45">
         <v>0.25</v>
       </c>
-      <c r="F5" s="102">
-        <v>1</v>
-      </c>
-      <c r="G5" s="52">
+      <c r="F5" s="75">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>0.172839506172839</v>
       </c>
-      <c r="H5" s="52">
+      <c r="H5">
         <v>0.11111111111111099</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5">
         <v>0.296296296296296</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5">
         <v>0.18518518518518501</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5">
         <v>0.25308641975308599</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5">
         <v>0.25925925925925902</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5">
         <v>0.29012345679012302</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5">
         <v>0.22839506172839499</v>
       </c>
       <c r="O5" s="20">
@@ -2183,31 +2207,31 @@
       <c r="E6" s="44">
         <v>0.25</v>
       </c>
-      <c r="F6" s="101">
-        <v>1</v>
-      </c>
-      <c r="G6" s="52">
-        <v>0</v>
-      </c>
-      <c r="H6" s="52">
-        <v>0</v>
-      </c>
-      <c r="I6" s="52">
-        <v>0</v>
-      </c>
-      <c r="J6" s="52">
-        <v>0</v>
-      </c>
-      <c r="K6" s="52">
-        <v>0</v>
-      </c>
-      <c r="L6" s="52">
-        <v>0</v>
-      </c>
-      <c r="M6" s="52">
-        <v>0</v>
-      </c>
-      <c r="N6" s="52">
+      <c r="F6" s="74">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
       <c r="O6" s="20">
@@ -2230,31 +2254,31 @@
       <c r="E7" s="44">
         <v>0.25</v>
       </c>
-      <c r="F7" s="101">
-        <v>1</v>
-      </c>
-      <c r="G7" s="52">
+      <c r="F7" s="74">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>0.16666666666666599</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7">
         <v>8.0246913580246895E-2</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.21604938271604901</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7">
         <v>0.12962962962962901</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.22839506172839499</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7">
         <v>0.28395061728394999</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.28395061728394999</v>
       </c>
-      <c r="N7" s="52">
+      <c r="N7">
         <v>0.21604938271604901</v>
       </c>
       <c r="O7" s="20">
@@ -2277,31 +2301,31 @@
       <c r="E8" s="44">
         <v>0.25</v>
       </c>
-      <c r="F8" s="101">
-        <v>1</v>
-      </c>
-      <c r="G8" s="52">
+      <c r="F8" s="74">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>0.16666666666666599</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8">
         <v>0.11111111111111099</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.209876543209876</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8">
         <v>0.19135802469135799</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.22839506172839499</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8">
         <v>0.28395061728394999</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.28395061728394999</v>
       </c>
-      <c r="N8" s="52">
+      <c r="N8">
         <v>0.22222222222222199</v>
       </c>
       <c r="O8" s="20">
@@ -2324,31 +2348,31 @@
       <c r="E9" s="44">
         <v>0.25</v>
       </c>
-      <c r="F9" s="101">
-        <v>1</v>
-      </c>
-      <c r="G9" s="52">
+      <c r="F9" s="74">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>0.172839506172839</v>
       </c>
-      <c r="H9" s="52">
+      <c r="H9">
         <v>0.11111111111111099</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9">
         <v>0.234567901234567</v>
       </c>
-      <c r="J9" s="52">
+      <c r="J9">
         <v>0.19135802469135799</v>
       </c>
-      <c r="K9" s="52">
+      <c r="K9">
         <v>0.234567901234567</v>
       </c>
-      <c r="L9" s="52">
+      <c r="L9">
         <v>0.28395061728394999</v>
       </c>
-      <c r="M9" s="52">
+      <c r="M9">
         <v>0.29012345679012302</v>
       </c>
-      <c r="N9" s="52">
+      <c r="N9">
         <v>0.22222222222222199</v>
       </c>
       <c r="O9" s="20">
@@ -2371,31 +2395,31 @@
       <c r="E10" s="43">
         <v>0.25</v>
       </c>
-      <c r="F10" s="100">
-        <v>1</v>
-      </c>
-      <c r="G10" s="52">
+      <c r="F10" s="73">
+        <v>1</v>
+      </c>
+      <c r="G10">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="H10" s="52">
-        <v>0</v>
-      </c>
-      <c r="I10" s="52">
-        <v>0</v>
-      </c>
-      <c r="J10" s="52">
-        <v>0</v>
-      </c>
-      <c r="K10" s="52">
-        <v>0</v>
-      </c>
-      <c r="L10" s="52">
-        <v>0</v>
-      </c>
-      <c r="M10" s="52">
-        <v>0</v>
-      </c>
-      <c r="N10" s="52">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
       <c r="O10" s="20">
@@ -2418,31 +2442,31 @@
       <c r="E11" s="44">
         <v>0.25</v>
       </c>
-      <c r="F11" s="101">
-        <v>1</v>
-      </c>
-      <c r="G11" s="52">
+      <c r="F11" s="74">
+        <v>1</v>
+      </c>
+      <c r="G11">
         <v>0.12962962962962901</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11">
         <v>5.5555555555555497E-2</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.25308641975308599</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11">
         <v>0.172839506172839</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.22222222222222199</v>
       </c>
-      <c r="L11" s="52">
+      <c r="L11">
         <v>0.27160493827160398</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.27160493827160398</v>
       </c>
-      <c r="N11" s="52">
+      <c r="N11">
         <v>0.19135802469135799</v>
       </c>
       <c r="O11" s="20">
@@ -2465,31 +2489,31 @@
       <c r="E12" s="44">
         <v>0.25</v>
       </c>
-      <c r="F12" s="101">
-        <v>1</v>
-      </c>
-      <c r="G12" s="52">
+      <c r="F12" s="74">
+        <v>1</v>
+      </c>
+      <c r="G12">
         <v>0.141975308641975</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12">
         <v>9.2592592592592504E-2</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.265432098765432</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12">
         <v>0.21604938271604901</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.22839506172839499</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12">
         <v>0.27160493827160398</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.27160493827160398</v>
       </c>
-      <c r="N12" s="52">
+      <c r="N12">
         <v>0.22839506172839499</v>
       </c>
       <c r="O12" s="20">
@@ -2512,7 +2536,7 @@
       <c r="E13" s="45">
         <v>0.25</v>
       </c>
-      <c r="F13" s="102">
+      <c r="F13" s="75">
         <v>1</v>
       </c>
       <c r="G13" s="13">
@@ -2624,7 +2648,7 @@
       <c r="E2" s="43">
         <v>0.25</v>
       </c>
-      <c r="F2" s="97">
+      <c r="F2" s="70">
         <v>1</v>
       </c>
       <c r="G2" s="7">
@@ -2671,31 +2695,31 @@
       <c r="E3" s="44">
         <v>0.25</v>
       </c>
-      <c r="F3" s="98">
-        <v>1</v>
-      </c>
-      <c r="G3" s="52">
+      <c r="F3" s="71">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>0.16666666666666599</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3">
         <v>6.7901234567901203E-2</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.27160493827160398</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3">
         <v>0.179012345679012</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3">
         <v>0.25925925925925902</v>
       </c>
-      <c r="L3" s="52">
+      <c r="L3">
         <v>0.30246913580246898</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.32098765432098703</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3">
         <v>0.25308641975308599</v>
       </c>
       <c r="O3" s="20">
@@ -2718,31 +2742,31 @@
       <c r="E4" s="44">
         <v>0.25</v>
       </c>
-      <c r="F4" s="98">
-        <v>1</v>
-      </c>
-      <c r="G4" s="52">
+      <c r="F4" s="71">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>0.16049382716049301</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4">
         <v>0.11111111111111099</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.25308641975308599</v>
       </c>
-      <c r="J4" s="52">
+      <c r="J4">
         <v>0.172839506172839</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4">
         <v>0.25308641975308599</v>
       </c>
-      <c r="L4" s="52">
+      <c r="L4">
         <v>0.30246913580246898</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.30246913580246898</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4">
         <v>0.25308641975308599</v>
       </c>
       <c r="O4" s="20">
@@ -2765,31 +2789,31 @@
       <c r="E5" s="45">
         <v>0.25</v>
       </c>
-      <c r="F5" s="99">
-        <v>1</v>
-      </c>
-      <c r="G5" s="52">
+      <c r="F5" s="72">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>0.172839506172839</v>
       </c>
-      <c r="H5" s="52">
+      <c r="H5">
         <v>0.11111111111111099</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5">
         <v>0.27160493827160398</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5">
         <v>0.18518518518518501</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5">
         <v>0.25925925925925902</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5">
         <v>0.30246913580246898</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5">
         <v>0.32098765432098703</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5">
         <v>0.25308641975308599</v>
       </c>
       <c r="O5" s="20">
@@ -2812,31 +2836,31 @@
       <c r="E6" s="44">
         <v>0.25</v>
       </c>
-      <c r="F6" s="98">
-        <v>1</v>
-      </c>
-      <c r="G6" s="52">
-        <v>0</v>
-      </c>
-      <c r="H6" s="52">
-        <v>0</v>
-      </c>
-      <c r="I6" s="52">
-        <v>0</v>
-      </c>
-      <c r="J6" s="52">
-        <v>0</v>
-      </c>
-      <c r="K6" s="52">
-        <v>0</v>
-      </c>
-      <c r="L6" s="52">
-        <v>0</v>
-      </c>
-      <c r="M6" s="52">
-        <v>0</v>
-      </c>
-      <c r="N6" s="52">
+      <c r="F6" s="71">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
       <c r="O6" s="20">
@@ -2859,31 +2883,31 @@
       <c r="E7" s="44">
         <v>0.25</v>
       </c>
-      <c r="F7" s="98">
-        <v>1</v>
-      </c>
-      <c r="G7" s="52">
+      <c r="F7" s="71">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>0.16049382716049301</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7">
         <v>0.104938271604938</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.21604938271604901</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7">
         <v>0.13580246913580199</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.22839506172839499</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7">
         <v>0.265432098765432</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.296296296296296</v>
       </c>
-      <c r="N7" s="52">
+      <c r="N7">
         <v>0.24691358024691301</v>
       </c>
       <c r="O7" s="20">
@@ -2906,31 +2930,31 @@
       <c r="E8" s="44">
         <v>0.25</v>
       </c>
-      <c r="F8" s="98">
-        <v>1</v>
-      </c>
-      <c r="G8" s="52">
+      <c r="F8" s="71">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>0.16049382716049301</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8">
         <v>0.13580246913580199</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.16666666666666599</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8">
         <v>0.179012345679012</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.234567901234567</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8">
         <v>0.25925925925925902</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.296296296296296</v>
       </c>
-      <c r="N8" s="52">
+      <c r="N8">
         <v>0.24691358024691301</v>
       </c>
       <c r="O8" s="20">
@@ -2953,31 +2977,31 @@
       <c r="E9" s="44">
         <v>0.25</v>
       </c>
-      <c r="F9" s="98">
-        <v>1</v>
-      </c>
-      <c r="G9" s="52">
+      <c r="F9" s="71">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>0.16049382716049301</v>
       </c>
-      <c r="H9" s="52">
+      <c r="H9">
         <v>0.13580246913580199</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9">
         <v>0.22222222222222199</v>
       </c>
-      <c r="J9" s="52">
+      <c r="J9">
         <v>0.179012345679012</v>
       </c>
-      <c r="K9" s="52">
+      <c r="K9">
         <v>0.234567901234567</v>
       </c>
-      <c r="L9" s="52">
+      <c r="L9">
         <v>0.265432098765432</v>
       </c>
-      <c r="M9" s="52">
+      <c r="M9">
         <v>0.296296296296296</v>
       </c>
-      <c r="N9" s="52">
+      <c r="N9">
         <v>0.24691358024691301</v>
       </c>
       <c r="O9" s="20">
@@ -3000,31 +3024,31 @@
       <c r="E10" s="43">
         <v>0.25</v>
       </c>
-      <c r="F10" s="97">
-        <v>1</v>
-      </c>
-      <c r="G10" s="52">
+      <c r="F10" s="70">
+        <v>1</v>
+      </c>
+      <c r="G10">
         <v>6.1728395061728296E-3</v>
       </c>
-      <c r="H10" s="52">
-        <v>0</v>
-      </c>
-      <c r="I10" s="52">
-        <v>0</v>
-      </c>
-      <c r="J10" s="52">
-        <v>0</v>
-      </c>
-      <c r="K10" s="52">
-        <v>0</v>
-      </c>
-      <c r="L10" s="52">
-        <v>0</v>
-      </c>
-      <c r="M10" s="52">
-        <v>0</v>
-      </c>
-      <c r="N10" s="52">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
       <c r="O10" s="20">
@@ -3047,31 +3071,31 @@
       <c r="E11" s="44">
         <v>0.25</v>
       </c>
-      <c r="F11" s="98">
-        <v>1</v>
-      </c>
-      <c r="G11" s="52">
+      <c r="F11" s="71">
+        <v>1</v>
+      </c>
+      <c r="G11">
         <v>0.12962962962962901</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11">
         <v>4.9382716049382699E-2</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.27160493827160398</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11">
         <v>0.179012345679012</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.234567901234567</v>
       </c>
-      <c r="L11" s="52">
+      <c r="L11">
         <v>0.25308641975308599</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.30246913580246898</v>
       </c>
-      <c r="N11" s="52">
+      <c r="N11">
         <v>0.21604938271604901</v>
       </c>
       <c r="O11" s="20">
@@ -3094,31 +3118,31 @@
       <c r="E12" s="44">
         <v>0.25</v>
       </c>
-      <c r="F12" s="98">
-        <v>1</v>
-      </c>
-      <c r="G12" s="52">
+      <c r="F12" s="71">
+        <v>1</v>
+      </c>
+      <c r="G12">
         <v>0.13580246913580199</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12">
         <v>9.2592592592592504E-2</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.28395061728394999</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12">
         <v>0.21604938271604901</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.24074074074074001</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12">
         <v>0.25925925925925902</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.296296296296296</v>
       </c>
-      <c r="N12" s="52">
+      <c r="N12">
         <v>0.234567901234567</v>
       </c>
       <c r="O12" s="20">
@@ -3141,7 +3165,7 @@
       <c r="E13" s="45">
         <v>0.25</v>
       </c>
-      <c r="F13" s="99">
+      <c r="F13" s="72">
         <v>1</v>
       </c>
       <c r="G13" s="13">
@@ -3307,7 +3331,7 @@
       <c r="C3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="44">
@@ -3319,31 +3343,31 @@
       <c r="G3" s="10">
         <v>0.28658536585365801</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3">
         <v>0.49390243902439002</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.55487804878048697</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3">
         <v>0.707317073170731</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3">
         <v>0.71341463414634099</v>
       </c>
-      <c r="L3" s="52">
+      <c r="L3">
         <v>0.73780487804878003</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.81707317073170704</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3">
         <v>0.82926829268292601</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3">
         <v>0.75609756097560898</v>
       </c>
-      <c r="P3" s="52">
+      <c r="P3">
         <v>0.76829268292682895</v>
       </c>
       <c r="Q3" s="20">
@@ -3360,7 +3384,7 @@
       <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="44">
@@ -3372,31 +3396,31 @@
       <c r="G4" s="10">
         <v>0.310975609756097</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4">
         <v>0.50609756097560898</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.55487804878048697</v>
       </c>
-      <c r="J4" s="52">
+      <c r="J4">
         <v>0.70121951219512102</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4">
         <v>0.71951219512195097</v>
       </c>
-      <c r="L4" s="52">
+      <c r="L4">
         <v>0.74390243902439002</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.82317073170731703</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4">
         <v>0.835365853658536</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4">
         <v>0.75</v>
       </c>
-      <c r="P4" s="52">
+      <c r="P4">
         <v>0.76219512195121897</v>
       </c>
       <c r="Q4" s="20">
@@ -3519,7 +3543,7 @@
       <c r="C7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="44">
@@ -3531,31 +3555,31 @@
       <c r="G7" s="10">
         <v>0.55487804878048697</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7">
         <v>0.57317073170731703</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.48170731707316999</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7">
         <v>0.78658536585365801</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.73170731707317005</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7">
         <v>0.71341463414634099</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.792682926829268</v>
       </c>
-      <c r="N7" s="52">
+      <c r="N7">
         <v>0.78658536585365801</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7">
         <v>0.12804878048780399</v>
       </c>
-      <c r="P7" s="52">
+      <c r="P7">
         <v>0.70121951219512102</v>
       </c>
       <c r="Q7" s="20">
@@ -3572,7 +3596,7 @@
       <c r="C8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="44">
@@ -3584,31 +3608,31 @@
       <c r="G8" s="10">
         <v>0.57317073170731703</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8">
         <v>0.60365853658536495</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.51219512195121897</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8">
         <v>0.78048780487804803</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.72560975609756095</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8">
         <v>0.72560975609756095</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.82926829268292601</v>
       </c>
-      <c r="N8" s="52">
+      <c r="N8">
         <v>0.82317073170731703</v>
       </c>
-      <c r="O8" s="52">
+      <c r="O8">
         <v>0.75609756097560898</v>
       </c>
-      <c r="P8" s="52">
+      <c r="P8">
         <v>0.80487804878048697</v>
       </c>
       <c r="Q8" s="20">
@@ -3690,31 +3714,31 @@
       <c r="G10" s="10">
         <v>0</v>
       </c>
-      <c r="H10" s="52">
-        <v>0</v>
-      </c>
-      <c r="I10" s="52">
-        <v>0</v>
-      </c>
-      <c r="J10" s="52">
-        <v>0</v>
-      </c>
-      <c r="K10" s="52">
-        <v>0</v>
-      </c>
-      <c r="L10" s="52">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>0.16463414634146301</v>
       </c>
-      <c r="M10" s="52">
-        <v>0</v>
-      </c>
-      <c r="N10" s="52">
-        <v>0</v>
-      </c>
-      <c r="O10" s="52">
-        <v>0</v>
-      </c>
-      <c r="P10" s="52">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10" s="20">
@@ -3731,7 +3755,7 @@
       <c r="C11" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="44">
@@ -3743,31 +3767,31 @@
       <c r="G11" s="10">
         <v>0.53048780487804803</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11">
         <v>0.55487804878048697</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.542682926829268</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11">
         <v>0.70121951219512102</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.73780487804878003</v>
       </c>
-      <c r="L11" s="52">
+      <c r="L11">
         <v>0.70121951219512102</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.82926829268292601</v>
       </c>
-      <c r="N11" s="52">
+      <c r="N11">
         <v>0.81097560975609695</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11">
         <v>0.207317073170731</v>
       </c>
-      <c r="P11" s="52">
+      <c r="P11">
         <v>0.70121951219512102</v>
       </c>
       <c r="Q11" s="20">
@@ -3784,7 +3808,7 @@
       <c r="C12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="44">
@@ -3796,31 +3820,31 @@
       <c r="G12" s="10">
         <v>0.542682926829268</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12">
         <v>0.55487804878048697</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.542682926829268</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12">
         <v>0.70121951219512102</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.73780487804878003</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12">
         <v>0.69512195121951204</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.82926829268292601</v>
       </c>
-      <c r="N12" s="52">
+      <c r="N12">
         <v>0.81707317073170704</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12">
         <v>0.74390243902439002</v>
       </c>
-      <c r="P12" s="52">
+      <c r="P12">
         <v>0.71341463414634099</v>
       </c>
       <c r="Q12" s="20">
@@ -4015,7 +4039,7 @@
       <c r="C3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="44">
@@ -4024,34 +4048,34 @@
       <c r="F3" s="24">
         <v>1</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3">
         <v>0.43</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3">
         <v>0.442</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.49</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3">
         <v>0.59399999999999997</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3">
         <v>0.622</v>
       </c>
-      <c r="L3" s="52">
+      <c r="L3">
         <v>0.628</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.73599999999999999</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3">
         <v>0.73399999999999999</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3">
         <v>0.52400000000000002</v>
       </c>
-      <c r="P3" s="52">
+      <c r="P3">
         <v>0.56399999999999995</v>
       </c>
       <c r="Q3" s="20">
@@ -4068,7 +4092,7 @@
       <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="44">
@@ -4077,34 +4101,34 @@
       <c r="F4" s="24">
         <v>1</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4">
         <v>0.42799999999999999</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.49399999999999999</v>
       </c>
-      <c r="J4" s="52">
+      <c r="J4">
         <v>0.59799999999999998</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4">
         <v>0.622</v>
       </c>
-      <c r="L4" s="52">
+      <c r="L4">
         <v>0.63200000000000001</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.73599999999999999</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4">
         <v>0.73399999999999999</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4">
         <v>0.53400000000000003</v>
       </c>
-      <c r="P4" s="52">
+      <c r="P4">
         <v>0.57599999999999996</v>
       </c>
       <c r="Q4" s="20">
@@ -4227,7 +4251,7 @@
       <c r="C7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="44">
@@ -4236,34 +4260,34 @@
       <c r="F7" s="24">
         <v>1</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7">
         <v>0.496</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7">
         <v>0.45400000000000001</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.49199999999999999</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.61799999999999999</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7">
         <v>0.57799999999999996</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.72</v>
       </c>
-      <c r="N7" s="52">
+      <c r="N7">
         <v>0.72799999999999998</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="P7" s="52">
+      <c r="P7">
         <v>0.55000000000000004</v>
       </c>
       <c r="Q7" s="20">
@@ -4280,7 +4304,7 @@
       <c r="C8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="44">
@@ -4289,34 +4313,34 @@
       <c r="F8" s="24">
         <v>1</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8">
         <v>0.496</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8">
         <v>0.48199999999999998</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.49199999999999999</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.622</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8">
         <v>0.60799999999999998</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.72</v>
       </c>
-      <c r="N8" s="52">
+      <c r="N8">
         <v>0.72799999999999998</v>
       </c>
-      <c r="O8" s="52">
+      <c r="O8">
         <v>0.51</v>
       </c>
-      <c r="P8" s="52">
+      <c r="P8">
         <v>0.56799999999999995</v>
       </c>
       <c r="Q8" s="20">
@@ -4439,7 +4463,7 @@
       <c r="C11" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="44">
@@ -4448,34 +4472,34 @@
       <c r="F11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11">
         <v>0.46</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.498</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11">
         <v>0.54600000000000004</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.60399999999999998</v>
       </c>
-      <c r="L11" s="52">
+      <c r="L11">
         <v>0.61</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.71199999999999997</v>
       </c>
-      <c r="N11" s="52">
+      <c r="N11">
         <v>0.71</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11">
         <v>0.24</v>
       </c>
-      <c r="P11" s="52">
+      <c r="P11">
         <v>0.54800000000000004</v>
       </c>
       <c r="Q11" s="20">
@@ -4492,7 +4516,7 @@
       <c r="C12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="44">
@@ -4501,34 +4525,34 @@
       <c r="F12" s="24">
         <v>1</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12">
         <v>0.47</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.498</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12">
         <v>0.54600000000000004</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.60399999999999998</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12">
         <v>0.622</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.71199999999999997</v>
       </c>
-      <c r="N12" s="52">
+      <c r="N12">
         <v>0.71</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12">
         <v>0.502</v>
       </c>
-      <c r="P12" s="52">
+      <c r="P12">
         <v>0.54800000000000004</v>
       </c>
       <c r="Q12" s="20">
@@ -4723,7 +4747,7 @@
       <c r="C3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="44">
@@ -4732,34 +4756,34 @@
       <c r="F3" s="24">
         <v>1</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3">
         <v>0.114</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3">
         <v>0.27200000000000002</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.308</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3">
         <v>0.29399999999999998</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3">
         <v>0.26800000000000002</v>
       </c>
-      <c r="L3" s="52">
+      <c r="L3">
         <v>0.30199999999999999</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.32800000000000001</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3">
         <v>0.32800000000000001</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3">
         <v>0.33</v>
       </c>
-      <c r="P3" s="52">
+      <c r="P3">
         <v>0.33400000000000002</v>
       </c>
       <c r="Q3" s="20">
@@ -4776,7 +4800,7 @@
       <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="44">
@@ -4785,34 +4809,34 @@
       <c r="F4" s="24">
         <v>1</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4">
         <v>0.224</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4">
         <v>0.28999999999999998</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.308</v>
       </c>
-      <c r="J4" s="52">
+      <c r="J4">
         <v>0.308</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4">
         <v>0.3</v>
       </c>
-      <c r="L4" s="52">
+      <c r="L4">
         <v>0.312</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.33</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4">
         <v>0.32800000000000001</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4">
         <v>0.32800000000000001</v>
       </c>
-      <c r="P4" s="52">
+      <c r="P4">
         <v>0.33200000000000002</v>
       </c>
       <c r="Q4" s="20">
@@ -4935,7 +4959,7 @@
       <c r="C7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="44">
@@ -4944,34 +4968,34 @@
       <c r="F7" s="24">
         <v>1</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7">
         <v>0.30399999999999999</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7">
         <v>0.224</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.318</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7">
         <v>0.27600000000000002</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.312</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.33200000000000002</v>
       </c>
-      <c r="N7" s="52">
+      <c r="N7">
         <v>0.33</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7">
         <v>1.2E-2</v>
       </c>
-      <c r="P7" s="52">
+      <c r="P7">
         <v>0.32600000000000001</v>
       </c>
       <c r="Q7" s="20">
@@ -4988,7 +5012,7 @@
       <c r="C8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="44">
@@ -4997,34 +5021,34 @@
       <c r="F8" s="24">
         <v>1</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8">
         <v>0.314</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8">
         <v>0.27800000000000002</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.316</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8">
         <v>0.30199999999999999</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.32</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8">
         <v>0.30199999999999999</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.32800000000000001</v>
       </c>
-      <c r="N8" s="52">
+      <c r="N8">
         <v>0.32800000000000001</v>
       </c>
-      <c r="O8" s="52">
+      <c r="O8">
         <v>0.32400000000000001</v>
       </c>
-      <c r="P8" s="52">
+      <c r="P8">
         <v>0.33</v>
       </c>
       <c r="Q8" s="20">
@@ -5147,7 +5171,7 @@
       <c r="C11" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="44">
@@ -5156,34 +5180,34 @@
       <c r="F11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11">
         <v>0.25</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11">
         <v>0.33</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.33</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11">
         <v>0.34599999999999997</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.32800000000000001</v>
       </c>
-      <c r="L11" s="52">
+      <c r="L11">
         <v>0.318</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.33600000000000002</v>
       </c>
-      <c r="N11" s="52">
+      <c r="N11">
         <v>0.33400000000000002</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11">
         <v>0.214</v>
       </c>
-      <c r="P11" s="52">
+      <c r="P11">
         <v>0.33400000000000002</v>
       </c>
       <c r="Q11" s="20">
@@ -5200,7 +5224,7 @@
       <c r="C12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="44">
@@ -5209,34 +5233,34 @@
       <c r="F12" s="24">
         <v>1</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12">
         <v>0.30199999999999999</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12">
         <v>0.33</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.33</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12">
         <v>0.32600000000000001</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.32400000000000001</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12">
         <v>0.32200000000000001</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.33</v>
       </c>
-      <c r="N12" s="52">
+      <c r="N12">
         <v>0.32800000000000001</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12">
         <v>0.33</v>
       </c>
-      <c r="P12" s="52">
+      <c r="P12">
         <v>0.32600000000000001</v>
       </c>
       <c r="Q12" s="20">
@@ -5430,7 +5454,7 @@
       <c r="C3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="44">
@@ -5439,31 +5463,31 @@
       <c r="F3" s="24">
         <v>1</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3">
         <v>0.141975308641975</v>
       </c>
       <c r="H3" s="2">
         <v>0.25925925925925902</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.172839506172839</v>
       </c>
       <c r="J3" s="2">
         <v>0.25925925925925902</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3">
         <v>0.29012345679012302</v>
       </c>
       <c r="L3" s="2">
         <v>0.29012345679012302</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.22839506172839499</v>
       </c>
       <c r="N3" s="2">
         <v>0.22839506172839499</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3">
         <v>0.27160493827160398</v>
       </c>
       <c r="P3" s="2">
@@ -5483,7 +5507,7 @@
       <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="44">
@@ -5492,31 +5516,31 @@
       <c r="F4" s="24">
         <v>1</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4">
         <v>0.141975308641975</v>
       </c>
       <c r="H4" s="2">
         <v>0.24691358024691301</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.16666666666666599</v>
       </c>
       <c r="J4" s="2">
         <v>0.25925925925925902</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4">
         <v>0.29012345679012302</v>
       </c>
       <c r="L4" s="2">
         <v>0.28395061728394999</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.22839506172839499</v>
       </c>
       <c r="N4" s="2">
         <v>0.22839506172839499</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4">
         <v>0.22222222222222199</v>
       </c>
       <c r="P4" s="2">
@@ -5642,7 +5666,7 @@
       <c r="C7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="44">
@@ -5651,31 +5675,31 @@
       <c r="F7" s="24">
         <v>1</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7">
         <v>0.18518518518518501</v>
       </c>
       <c r="H7" s="2">
         <v>0.27160493827160398</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.12345679012345601</v>
       </c>
       <c r="J7" s="2">
         <v>0.22839506172839499</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.27160493827160398</v>
       </c>
       <c r="L7" s="2">
         <v>0.265432098765432</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.24074074074074001</v>
       </c>
       <c r="N7" s="2">
         <v>0.234567901234567</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7">
         <v>9.2592592592592504E-2</v>
       </c>
       <c r="P7" s="2">
@@ -5695,7 +5719,7 @@
       <c r="C8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="44">
@@ -5704,31 +5728,31 @@
       <c r="F8" s="24">
         <v>1</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8">
         <v>0.179012345679012</v>
       </c>
       <c r="H8" s="2">
         <v>0.234567901234567</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.13580246913580199</v>
       </c>
       <c r="J8" s="2">
         <v>0.22839506172839499</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.265432098765432</v>
       </c>
       <c r="L8" s="2">
         <v>0.265432098765432</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.24074074074074001</v>
       </c>
       <c r="N8" s="2">
         <v>0.234567901234567</v>
       </c>
-      <c r="O8" s="52">
+      <c r="O8">
         <v>0.16666666666666599</v>
       </c>
       <c r="P8" s="2">
@@ -5854,7 +5878,7 @@
       <c r="C11" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="44">
@@ -5863,31 +5887,31 @@
       <c r="F11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11">
         <v>0.148148148148148</v>
       </c>
       <c r="H11" s="2">
         <v>0.24074074074074001</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.16666666666666599</v>
       </c>
       <c r="J11" s="2">
         <v>0.21604938271604901</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.25308641975308599</v>
       </c>
       <c r="L11" s="2">
         <v>0.27160493827160398</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.22839506172839499</v>
       </c>
       <c r="N11" s="2">
         <v>0.19753086419752999</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11">
         <v>0.16049382716049301</v>
       </c>
       <c r="P11" s="2">
@@ -5907,7 +5931,7 @@
       <c r="C12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="44">
@@ -5916,31 +5940,31 @@
       <c r="F12" s="24">
         <v>1</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12">
         <v>0.15432098765432001</v>
       </c>
       <c r="H12" s="2">
         <v>0.24074074074074001</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.203703703703703</v>
       </c>
       <c r="J12" s="2">
         <v>0.22222222222222199</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.25308641975308599</v>
       </c>
       <c r="L12" s="2">
         <v>0.27160493827160398</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.24691358024691301</v>
       </c>
       <c r="N12" s="2">
         <v>0.234567901234567</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12">
         <v>0.19753086419752999</v>
       </c>
       <c r="P12" s="2">
@@ -6010,7 +6034,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E88DB91-37ED-AC45-B0F9-ADE8D8AC3799}">
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" customWidth="1"/>
@@ -6033,7 +6057,7 @@
     <col min="21" max="21" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -6098,802 +6122,851 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="55">
-        <v>1</v>
-      </c>
-      <c r="B2" s="85" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" s="36">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="58">
-        <v>1</v>
-      </c>
-      <c r="F2" s="87">
-        <v>1</v>
-      </c>
-      <c r="G2" s="62">
+      <c r="E2" s="8">
+        <v>1</v>
+      </c>
+      <c r="F2" s="23">
+        <v>1</v>
+      </c>
+      <c r="G2" s="57">
         <v>0.114</v>
       </c>
-      <c r="H2" s="56">
+      <c r="H2" s="6">
         <v>0.114</v>
       </c>
-      <c r="I2" s="86">
+      <c r="I2" s="7">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="J2" s="56">
-        <v>0</v>
-      </c>
-      <c r="K2" s="86">
-        <v>0</v>
-      </c>
-      <c r="L2" s="56">
+      <c r="J2" s="6">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6">
         <v>0.09</v>
       </c>
-      <c r="M2" s="86">
+      <c r="M2" s="7">
         <v>0.13200000000000001</v>
       </c>
-      <c r="N2" s="56">
+      <c r="N2" s="6">
         <v>0.27200000000000002</v>
       </c>
-      <c r="O2" s="86">
-        <v>0</v>
-      </c>
-      <c r="P2" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="86">
-        <v>0</v>
-      </c>
-      <c r="R2" s="56">
-        <v>0</v>
-      </c>
-      <c r="S2" s="86">
-        <v>0</v>
-      </c>
-      <c r="T2" s="56">
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="6">
+        <v>0</v>
+      </c>
+      <c r="S2" s="7">
+        <v>0</v>
+      </c>
+      <c r="T2" s="6">
         <v>2E-3</v>
       </c>
-      <c r="U2" s="85">
+      <c r="U2" s="19">
         <v>0.08</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="64">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" s="37">
         <v>2</v>
       </c>
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="89" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="67">
-        <v>1</v>
-      </c>
-      <c r="F3" s="90">
-        <v>1</v>
-      </c>
-      <c r="G3" s="71">
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="24">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
         <v>0.11799999999999999</v>
       </c>
-      <c r="H3" s="65">
+      <c r="H3" s="2">
         <v>0.11600000000000001</v>
       </c>
-      <c r="I3" s="91">
+      <c r="I3">
         <v>0.26</v>
       </c>
-      <c r="J3" s="65">
+      <c r="J3" s="2">
         <v>0.218</v>
       </c>
-      <c r="K3" s="91">
+      <c r="K3">
         <v>0.26600000000000001</v>
       </c>
-      <c r="L3" s="65">
+      <c r="L3" s="2">
         <v>0.254</v>
       </c>
-      <c r="M3" s="91">
+      <c r="M3">
         <v>0.222</v>
       </c>
-      <c r="N3" s="65">
+      <c r="N3" s="2">
         <v>0.27400000000000002</v>
       </c>
-      <c r="O3" s="91">
+      <c r="O3">
         <v>0.28799999999999998</v>
       </c>
-      <c r="P3" s="65">
+      <c r="P3" s="2">
         <v>0.28000000000000003</v>
       </c>
-      <c r="Q3" s="91">
+      <c r="Q3">
         <v>0.33200000000000002</v>
       </c>
-      <c r="R3" s="65">
+      <c r="R3" s="2">
         <v>0.33</v>
       </c>
-      <c r="S3" s="91">
+      <c r="S3">
         <v>0.33</v>
       </c>
-      <c r="T3" s="65">
+      <c r="T3" s="2">
         <v>0.30599999999999999</v>
       </c>
-      <c r="U3" s="88">
+      <c r="U3" s="20">
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64">
+    <row r="4" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="37">
         <v>3</v>
       </c>
-      <c r="B4" s="88" t="s">
+      <c r="B4" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="89" t="s">
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="73">
-        <v>1</v>
-      </c>
-      <c r="F4" s="92">
-        <v>1</v>
-      </c>
-      <c r="G4" s="77">
+      <c r="E4" s="14">
+        <v>1</v>
+      </c>
+      <c r="F4" s="25">
+        <v>1</v>
+      </c>
+      <c r="G4" s="65">
         <v>0.222</v>
       </c>
-      <c r="H4" s="93">
+      <c r="H4" s="12">
         <v>0.224</v>
       </c>
-      <c r="I4" s="83">
+      <c r="I4" s="13">
         <v>0.26400000000000001</v>
       </c>
-      <c r="J4" s="93">
+      <c r="J4" s="12">
         <v>0.248</v>
       </c>
-      <c r="K4" s="83">
+      <c r="K4" s="13">
         <v>0.26800000000000002</v>
       </c>
-      <c r="L4" s="93">
+      <c r="L4" s="12">
         <v>0.27800000000000002</v>
       </c>
-      <c r="M4" s="83">
+      <c r="M4" s="13">
         <v>0.252</v>
       </c>
-      <c r="N4" s="93">
+      <c r="N4" s="12">
         <v>0.28399999999999997</v>
       </c>
-      <c r="O4" s="83">
+      <c r="O4" s="13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="P4" s="93">
+      <c r="P4" s="12">
         <v>0.28000000000000003</v>
       </c>
-      <c r="Q4" s="83">
+      <c r="Q4" s="13">
         <v>0.32400000000000001</v>
       </c>
-      <c r="R4" s="93">
+      <c r="R4" s="12">
         <v>0.33200000000000002</v>
       </c>
-      <c r="S4" s="83">
+      <c r="S4" s="13">
         <v>0.33200000000000002</v>
       </c>
-      <c r="T4" s="93">
+      <c r="T4" s="12">
         <v>0.32</v>
       </c>
-      <c r="U4" s="84">
+      <c r="U4" s="18">
         <v>0.32</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79">
+    <row r="5" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="46">
         <v>4</v>
       </c>
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="95" t="s">
+      <c r="C5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="73">
-        <v>1</v>
-      </c>
-      <c r="F5" s="92">
-        <v>1</v>
-      </c>
-      <c r="G5" s="96">
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
+      <c r="F5" s="25">
+        <v>1</v>
+      </c>
+      <c r="G5" s="69">
         <v>0.14799999999999999</v>
       </c>
-      <c r="H5" s="80">
+      <c r="H5" s="26">
         <v>0.15</v>
       </c>
-      <c r="I5" s="95">
+      <c r="I5" s="21">
         <v>0.26200000000000001</v>
       </c>
-      <c r="J5" s="80">
+      <c r="J5" s="26">
         <v>0.22600000000000001</v>
       </c>
-      <c r="K5" s="95">
+      <c r="K5" s="21">
         <v>0.26800000000000002</v>
       </c>
-      <c r="L5" s="80">
+      <c r="L5" s="26">
         <v>0.254</v>
       </c>
-      <c r="M5" s="95">
+      <c r="M5" s="21">
         <v>0.224</v>
       </c>
-      <c r="N5" s="80">
+      <c r="N5" s="26">
         <v>0.27400000000000002</v>
       </c>
-      <c r="O5" s="95">
+      <c r="O5" s="21">
         <v>0.28799999999999998</v>
       </c>
-      <c r="P5" s="80">
+      <c r="P5" s="26">
         <v>0.28000000000000003</v>
       </c>
-      <c r="Q5" s="95">
+      <c r="Q5" s="21">
         <v>0.32200000000000001</v>
       </c>
-      <c r="R5" s="80">
+      <c r="R5" s="26">
         <v>0.33</v>
       </c>
-      <c r="S5" s="95">
+      <c r="S5" s="21">
         <v>0.33</v>
       </c>
-      <c r="T5" s="80">
+      <c r="T5" s="26">
         <v>0.308</v>
       </c>
-      <c r="U5" s="94">
+      <c r="U5" s="22">
         <v>0.30199999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="64">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="37">
         <v>5</v>
       </c>
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="86" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="57" t="s">
+      <c r="C6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="58">
-        <v>1</v>
-      </c>
-      <c r="F6" s="87">
-        <v>1</v>
-      </c>
-      <c r="G6" s="71">
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="23">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
         <v>2E-3</v>
       </c>
-      <c r="H6" s="65">
+      <c r="H6" s="2">
         <v>2E-3</v>
       </c>
-      <c r="I6" s="91">
-        <v>0</v>
-      </c>
-      <c r="J6" s="65">
-        <v>0</v>
-      </c>
-      <c r="K6" s="91">
-        <v>0</v>
-      </c>
-      <c r="L6" s="65">
-        <v>0</v>
-      </c>
-      <c r="M6" s="91">
-        <v>0</v>
-      </c>
-      <c r="N6" s="65">
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
         <v>0.04</v>
       </c>
-      <c r="O6" s="91">
-        <v>0</v>
-      </c>
-      <c r="P6" s="65">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="91">
-        <v>0</v>
-      </c>
-      <c r="R6" s="65">
-        <v>0</v>
-      </c>
-      <c r="S6" s="91">
-        <v>0</v>
-      </c>
-      <c r="T6" s="65">
-        <v>0</v>
-      </c>
-      <c r="U6" s="88">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="20">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="64">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="37">
         <v>6</v>
       </c>
-      <c r="B7" s="88" t="s">
+      <c r="B7" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="66" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="67">
-        <v>1</v>
-      </c>
-      <c r="F7" s="90">
-        <v>1</v>
-      </c>
-      <c r="G7" s="71">
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="24">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4">
         <v>0.26200000000000001</v>
       </c>
-      <c r="H7" s="65">
+      <c r="H7" s="2">
         <v>0.26200000000000001</v>
       </c>
-      <c r="I7" s="91">
+      <c r="I7">
         <v>0.27400000000000002</v>
       </c>
-      <c r="J7" s="65">
+      <c r="J7" s="2">
         <v>0.20599999999999999</v>
       </c>
-      <c r="K7" s="91">
+      <c r="K7">
         <v>0.28199999999999997</v>
       </c>
-      <c r="L7" s="65">
+      <c r="L7" s="2">
         <v>0.26</v>
       </c>
-      <c r="M7" s="91">
+      <c r="M7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N7" s="65">
+      <c r="N7" s="2">
         <v>0.25</v>
       </c>
-      <c r="O7" s="91">
+      <c r="O7">
         <v>0.29799999999999999</v>
       </c>
-      <c r="P7" s="65">
+      <c r="P7" s="2">
         <v>0.29199999999999998</v>
       </c>
-      <c r="Q7" s="91">
+      <c r="Q7">
         <v>0.35399999999999998</v>
       </c>
-      <c r="R7" s="65">
+      <c r="R7" s="2">
         <v>0.06</v>
       </c>
-      <c r="S7" s="91">
+      <c r="S7">
         <v>0.32600000000000001</v>
       </c>
-      <c r="T7" s="65">
+      <c r="T7" s="2">
         <v>0.23200000000000001</v>
       </c>
-      <c r="U7" s="88">
+      <c r="U7" s="20">
         <v>0.214</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="64">
+    <row r="8" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37">
         <v>7</v>
       </c>
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="66" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="73">
-        <v>1</v>
-      </c>
-      <c r="F8" s="92">
-        <v>1</v>
-      </c>
-      <c r="G8" s="77">
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="25">
+        <v>1</v>
+      </c>
+      <c r="G8" s="65">
         <v>0.27400000000000002</v>
       </c>
-      <c r="H8" s="65">
+      <c r="H8" s="2">
         <v>0.27400000000000002</v>
       </c>
-      <c r="I8" s="91">
+      <c r="I8">
         <v>0.27400000000000002</v>
       </c>
-      <c r="J8" s="65">
+      <c r="J8" s="2">
         <v>0.24199999999999999</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8">
         <v>0.28000000000000003</v>
       </c>
-      <c r="L8" s="65">
+      <c r="L8" s="2">
         <v>0.29799999999999999</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N8" s="65">
+      <c r="N8" s="2">
         <v>0.27800000000000002</v>
       </c>
-      <c r="O8" s="91">
+      <c r="O8">
         <v>0.29199999999999998</v>
       </c>
-      <c r="P8" s="65">
+      <c r="P8" s="2">
         <v>0.28799999999999998</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8">
         <v>0.32800000000000001</v>
       </c>
-      <c r="R8" s="65">
+      <c r="R8" s="2">
         <v>0.32200000000000001</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8">
         <v>0.33</v>
       </c>
-      <c r="T8" s="65">
+      <c r="T8" s="2">
         <v>0.28599999999999998</v>
       </c>
-      <c r="U8" s="88">
+      <c r="U8" s="20">
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="79">
+    <row r="9" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="46">
         <v>8</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="95" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="81" t="s">
+      <c r="C9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="73">
-        <v>1</v>
-      </c>
-      <c r="F9" s="92">
-        <v>1</v>
-      </c>
-      <c r="G9" s="71">
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
+      <c r="F9" s="25">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
         <v>0.27</v>
       </c>
-      <c r="H9" s="80">
+      <c r="H9" s="26">
         <v>0.27</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="21">
         <v>0.27400000000000002</v>
       </c>
-      <c r="J9" s="80">
+      <c r="J9" s="26">
         <v>0.20799999999999999</v>
       </c>
-      <c r="K9" s="95">
+      <c r="K9" s="21">
         <v>0.28000000000000003</v>
       </c>
-      <c r="L9" s="80">
+      <c r="L9" s="26">
         <v>0.26800000000000002</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="21">
         <v>0.28599999999999998</v>
       </c>
-      <c r="N9" s="80">
+      <c r="N9" s="26">
         <v>0.254</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="21">
         <v>0.29199999999999998</v>
       </c>
-      <c r="P9" s="80">
+      <c r="P9" s="26">
         <v>0.28599999999999998</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="21">
         <v>0.32800000000000001</v>
       </c>
-      <c r="R9" s="80">
+      <c r="R9" s="26">
         <v>0.318</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="21">
         <v>0.32600000000000001</v>
       </c>
-      <c r="T9" s="80">
+      <c r="T9" s="26">
         <v>0.23200000000000001</v>
       </c>
-      <c r="U9" s="94">
+      <c r="U9" s="22">
         <v>0.27800000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="55">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" s="36">
         <v>9</v>
       </c>
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="86" t="s">
+      <c r="C10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="58">
-        <v>1</v>
-      </c>
-      <c r="F10" s="87">
-        <v>1</v>
-      </c>
-      <c r="G10" s="62">
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="23">
+        <v>1</v>
+      </c>
+      <c r="G10" s="57">
         <v>1.6E-2</v>
       </c>
-      <c r="H10" s="65">
+      <c r="H10" s="2">
         <v>1.6E-2</v>
       </c>
-      <c r="I10" s="91">
-        <v>0</v>
-      </c>
-      <c r="J10" s="65">
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
         <v>2E-3</v>
       </c>
-      <c r="K10" s="91">
-        <v>0</v>
-      </c>
-      <c r="L10" s="65">
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
         <v>2E-3</v>
       </c>
-      <c r="M10" s="91">
+      <c r="M10">
         <v>2E-3</v>
       </c>
-      <c r="N10" s="65">
+      <c r="N10" s="2">
         <v>1.6E-2</v>
       </c>
-      <c r="O10" s="91">
+      <c r="O10">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="P10" s="65">
+      <c r="P10" s="2">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="Q10" s="91">
-        <v>0</v>
-      </c>
-      <c r="R10" s="65">
-        <v>0</v>
-      </c>
-      <c r="S10" s="91">
-        <v>0</v>
-      </c>
-      <c r="T10" s="65">
-        <v>0</v>
-      </c>
-      <c r="U10" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="64">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="37">
         <v>10</v>
       </c>
-      <c r="B11" s="88" t="s">
+      <c r="B11" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="89" t="s">
+      <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="67">
-        <v>1</v>
-      </c>
-      <c r="F11" s="90">
-        <v>1</v>
-      </c>
-      <c r="G11" s="71">
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="24">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4">
         <v>0.03</v>
       </c>
-      <c r="H11" s="65">
+      <c r="H11" s="2">
         <v>0.03</v>
       </c>
-      <c r="I11" s="91">
+      <c r="I11">
         <v>0.28399999999999997</v>
       </c>
-      <c r="J11" s="65">
+      <c r="J11" s="2">
         <v>0.3</v>
       </c>
-      <c r="K11" s="91">
+      <c r="K11">
         <v>0.26400000000000001</v>
       </c>
-      <c r="L11" s="65">
+      <c r="L11" s="2">
         <v>0.126</v>
       </c>
-      <c r="M11" s="91">
+      <c r="M11">
         <v>0.14799999999999999</v>
       </c>
-      <c r="N11" s="65">
+      <c r="N11" s="2">
         <v>0.22600000000000001</v>
       </c>
-      <c r="O11" s="91">
+      <c r="O11">
         <v>0.22</v>
       </c>
-      <c r="P11" s="65">
+      <c r="P11" s="2">
         <v>0.218</v>
       </c>
-      <c r="Q11" s="91">
+      <c r="Q11">
         <v>0.372</v>
       </c>
-      <c r="R11" s="65">
+      <c r="R11" s="2">
         <v>0.318</v>
       </c>
-      <c r="S11" s="91">
+      <c r="S11">
         <v>0.33400000000000002</v>
       </c>
-      <c r="T11" s="65">
+      <c r="T11" s="2">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="U11" s="88">
+      <c r="U11" s="20">
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="64">
+    <row r="12" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37">
         <v>11</v>
       </c>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="89" t="s">
+      <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="66" t="s">
+      <c r="D12" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="73">
-        <v>1</v>
-      </c>
-      <c r="F12" s="92">
-        <v>1</v>
-      </c>
-      <c r="G12" s="77">
+      <c r="E12" s="14">
+        <v>1</v>
+      </c>
+      <c r="F12" s="25">
+        <v>1</v>
+      </c>
+      <c r="G12" s="65">
         <v>0.22800000000000001</v>
       </c>
-      <c r="H12" s="65">
+      <c r="H12" s="2">
         <v>0.22800000000000001</v>
       </c>
-      <c r="I12" s="91">
+      <c r="I12">
         <v>0.26400000000000001</v>
       </c>
-      <c r="J12" s="65">
+      <c r="J12" s="2">
         <v>0.29799999999999999</v>
       </c>
-      <c r="K12" s="91">
+      <c r="K12">
         <v>0.248</v>
       </c>
-      <c r="L12" s="65">
+      <c r="L12" s="2">
         <v>0.28000000000000003</v>
       </c>
-      <c r="M12" s="91">
+      <c r="M12">
         <v>0.21</v>
       </c>
-      <c r="N12" s="65">
+      <c r="N12" s="2">
         <v>0.23599999999999999</v>
       </c>
-      <c r="O12" s="91">
+      <c r="O12">
         <v>0.20799999999999999</v>
       </c>
-      <c r="P12" s="65">
+      <c r="P12" s="2">
         <v>0.20399999999999999</v>
       </c>
-      <c r="Q12" s="91">
+      <c r="Q12">
         <v>0.32200000000000001</v>
       </c>
-      <c r="R12" s="65">
+      <c r="R12" s="2">
         <v>0.33</v>
       </c>
-      <c r="S12" s="91">
+      <c r="S12">
         <v>0.32600000000000001</v>
       </c>
-      <c r="T12" s="65">
+      <c r="T12" s="2">
         <v>6.2E-2</v>
       </c>
-      <c r="U12" s="88">
+      <c r="U12" s="20">
         <v>0.30199999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="79">
+    <row r="13" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="46">
         <v>12</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="81" t="s">
+      <c r="D13" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="73">
-        <v>1</v>
-      </c>
-      <c r="F13" s="92">
-        <v>1</v>
-      </c>
-      <c r="G13" s="83">
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="25">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13">
         <v>0.2</v>
       </c>
-      <c r="H13" s="80">
+      <c r="H13" s="26">
         <v>0.2</v>
       </c>
-      <c r="I13" s="95">
+      <c r="I13" s="21">
         <v>0.26400000000000001</v>
       </c>
-      <c r="J13" s="80">
+      <c r="J13" s="26">
         <v>0.29799999999999999</v>
       </c>
-      <c r="K13" s="95">
+      <c r="K13" s="21">
         <v>0.248</v>
       </c>
-      <c r="L13" s="80">
+      <c r="L13" s="26">
         <v>0.28000000000000003</v>
       </c>
-      <c r="M13" s="95">
+      <c r="M13" s="21">
         <v>0.20799999999999999</v>
       </c>
-      <c r="N13" s="80">
+      <c r="N13" s="26">
         <v>0.23</v>
       </c>
-      <c r="O13" s="95">
+      <c r="O13" s="21">
         <v>0.20799999999999999</v>
       </c>
-      <c r="P13" s="80">
+      <c r="P13" s="26">
         <v>0.20399999999999999</v>
       </c>
-      <c r="Q13" s="95">
+      <c r="Q13" s="21">
         <v>0.32200000000000001</v>
       </c>
-      <c r="R13" s="80">
+      <c r="R13" s="26">
         <v>0.33</v>
       </c>
-      <c r="S13" s="95">
+      <c r="S13" s="21">
         <v>0.32600000000000001</v>
       </c>
-      <c r="T13" s="80">
+      <c r="T13" s="26">
         <v>6.2E-2</v>
       </c>
-      <c r="U13" s="94">
+      <c r="U13" s="22">
         <v>0.28199999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G14" s="4">
+        <f>MAX(G2:G13)</f>
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" ref="H14:U14" si="0">MAX(H2:H13)</f>
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="O14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="P14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="Q14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.372</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="S14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="T14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.32</v>
+      </c>
+      <c r="U14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.32</v>
+      </c>
+      <c r="V14" s="76">
+        <f>MAX(G14:U14)</f>
+        <v>0.372</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6902,7 +6975,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB92485-4A32-3C43-82C3-858D3065D142}">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -6925,7 +6998,7 @@
     <col min="21" max="21" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -6990,7 +7063,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="36">
         <v>1</v>
       </c>
@@ -7055,7 +7128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="37">
         <v>2</v>
       </c>
@@ -7120,7 +7193,7 @@
         <v>0.24691358024691301</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37">
         <v>3</v>
       </c>
@@ -7185,7 +7258,7 @@
         <v>0.25308641975308599</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="46">
         <v>4</v>
       </c>
@@ -7250,7 +7323,7 @@
         <v>0.25308641975308599</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="37">
         <v>5</v>
       </c>
@@ -7315,7 +7388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="37">
         <v>6</v>
       </c>
@@ -7380,7 +7453,7 @@
         <v>0.29012345679012302</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37">
         <v>7</v>
       </c>
@@ -7445,7 +7518,7 @@
         <v>0.265432098765432</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="46">
         <v>8</v>
       </c>
@@ -7510,7 +7583,7 @@
         <v>0.29012345679012302</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="36">
         <v>9</v>
       </c>
@@ -7575,7 +7648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="37">
         <v>10</v>
       </c>
@@ -7640,7 +7713,7 @@
         <v>0.25925925925925902</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>11</v>
       </c>
@@ -7705,7 +7778,7 @@
         <v>0.28395061728394999</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38">
         <v>12</v>
       </c>
@@ -7768,6 +7841,72 @@
       </c>
       <c r="U13" s="22">
         <v>0.29012345679012302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G14" s="4">
+        <f>MAX(G2:G13)</f>
+        <v>0.179012345679012</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" ref="H14:U14" si="0">MAX(H2:H13)</f>
+        <v>0.179012345679012</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.117283950617283</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.296296296296296</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.234567901234567</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.28395061728394999</v>
+      </c>
+      <c r="N14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.296296296296296</v>
+      </c>
+      <c r="O14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.24074074074074001</v>
+      </c>
+      <c r="P14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.234567901234567</v>
+      </c>
+      <c r="Q14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.141975308641975</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.234567901234567</v>
+      </c>
+      <c r="S14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.29012345679012302</v>
+      </c>
+      <c r="T14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.24691358024691301</v>
+      </c>
+      <c r="U14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.29012345679012302</v>
+      </c>
+      <c r="V14" s="76">
+        <f>MAX(G14:U14)</f>
+        <v>0.296296296296296</v>
       </c>
     </row>
   </sheetData>
@@ -7777,7 +7916,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36D4C86E-4733-0A4F-9B87-3260BC1D994C}">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -7800,7 +7939,7 @@
     <col min="21" max="21" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -7865,7 +8004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -7930,14 +8069,14 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="37" t="s">
@@ -7995,14 +8134,14 @@
         <v>0.58399999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>3</v>
       </c>
       <c r="B4" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="37" t="s">
@@ -8060,11 +8199,11 @@
         <v>0.58399999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53">
+    <row r="5" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="52">
         <v>4</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="53" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="21" t="s">
@@ -8125,14 +8264,14 @@
         <v>0.58399999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>5</v>
       </c>
       <c r="B6" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="37" t="s">
@@ -8190,14 +8329,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="37" t="s">
@@ -8255,14 +8394,14 @@
         <v>0.56599999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>7</v>
       </c>
       <c r="B8" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="37" t="s">
@@ -8320,11 +8459,11 @@
         <v>0.56799999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53">
+    <row r="9" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="52">
         <v>8</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="53" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="21" t="s">
@@ -8385,7 +8524,7 @@
         <v>0.56799999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -8450,14 +8589,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>10</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="37" t="s">
@@ -8515,14 +8654,14 @@
         <v>0.54200000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>11</v>
       </c>
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="37" t="s">
@@ -8580,11 +8719,11 @@
         <v>0.56399999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53">
+    <row r="13" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="52">
         <v>12</v>
       </c>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="53" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="21" t="s">
@@ -8643,6 +8782,72 @@
       </c>
       <c r="U13" s="32">
         <v>0.56399999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G14" s="4">
+        <f>MAX(G2:G13)</f>
+        <v>0.498</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" ref="H14:U14" si="0">MAX(H2:H13)</f>
+        <v>0.498</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="N14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="O14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.73399999999999999</v>
+      </c>
+      <c r="P14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.74</v>
+      </c>
+      <c r="Q14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="S14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="T14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="U14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="V14" s="76">
+        <f>MAX(G14:U14)</f>
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -8652,7 +8857,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{068F4A57-62AA-4947-B347-625F6A9C32EB}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -8664,7 +8869,7 @@
     <col min="7" max="17" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="159" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -8717,7 +8922,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="36">
         <v>1</v>
       </c>
@@ -8770,7 +8975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="37">
         <v>2</v>
       </c>
@@ -8780,7 +8985,7 @@
       <c r="C3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="44">
@@ -8792,38 +8997,38 @@
       <c r="G3" s="10">
         <v>0.28658536585365801</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3">
         <v>0.49390243902439002</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.55487804878048697</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3">
         <v>0.707317073170731</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3">
         <v>0.71341463414634099</v>
       </c>
-      <c r="L3" s="52">
+      <c r="L3">
         <v>0.73780487804878003</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.81707317073170704</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3">
         <v>0.82926829268292601</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3">
         <v>0.75609756097560898</v>
       </c>
-      <c r="P3" s="52">
+      <c r="P3">
         <v>0.76829268292682895</v>
       </c>
       <c r="Q3" s="20">
         <v>0.68292682926829196</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="37">
         <v>3</v>
       </c>
@@ -8833,7 +9038,7 @@
       <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="44">
@@ -8845,38 +9050,38 @@
       <c r="G4" s="10">
         <v>0.310975609756097</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4">
         <v>0.50609756097560898</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.55487804878048697</v>
       </c>
-      <c r="J4" s="52">
+      <c r="J4">
         <v>0.70121951219512102</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4">
         <v>0.71951219512195097</v>
       </c>
-      <c r="L4" s="52">
+      <c r="L4">
         <v>0.74390243902439002</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.82317073170731703</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4">
         <v>0.835365853658536</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4">
         <v>0.75</v>
       </c>
-      <c r="P4" s="52">
+      <c r="P4">
         <v>0.76219512195121897</v>
       </c>
       <c r="Q4" s="20">
         <v>0.68292682926829196</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>4</v>
       </c>
@@ -8929,7 +9134,7 @@
         <v>0.68292682926829196</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="36">
         <v>5</v>
       </c>
@@ -8982,7 +9187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="37">
         <v>6</v>
       </c>
@@ -8992,7 +9197,7 @@
       <c r="C7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="44">
@@ -9004,38 +9209,38 @@
       <c r="G7" s="10">
         <v>0.55487804878048697</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7">
         <v>0.57317073170731703</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.48170731707316999</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7">
         <v>0.78658536585365801</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.73170731707317005</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7">
         <v>0.71341463414634099</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.792682926829268</v>
       </c>
-      <c r="N7" s="52">
+      <c r="N7">
         <v>0.78658536585365801</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7">
         <v>0.12804878048780399</v>
       </c>
-      <c r="P7" s="52">
+      <c r="P7">
         <v>0.70121951219512102</v>
       </c>
       <c r="Q7" s="20">
         <v>0.63414634146341398</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="37">
         <v>7</v>
       </c>
@@ -9045,7 +9250,7 @@
       <c r="C8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="44">
@@ -9057,38 +9262,38 @@
       <c r="G8" s="10">
         <v>0.57317073170731703</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8">
         <v>0.71365853658536504</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.51219512195121897</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8">
         <v>0.78048780487804803</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.72560975609756095</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8">
         <v>0.72560975609756095</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.82926829268292601</v>
       </c>
-      <c r="N8" s="52">
+      <c r="N8">
         <v>0.82317073170731703</v>
       </c>
-      <c r="O8" s="52">
+      <c r="O8">
         <v>0.75609756097560898</v>
       </c>
-      <c r="P8" s="52">
+      <c r="P8">
         <v>0.80887804878048697</v>
       </c>
       <c r="Q8" s="20">
         <v>0.63414634146341398</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="38">
         <v>8</v>
       </c>
@@ -9141,7 +9346,7 @@
         <v>0.63414634146341398</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="36">
         <v>9</v>
       </c>
@@ -9163,38 +9368,38 @@
       <c r="G10" s="10">
         <v>0</v>
       </c>
-      <c r="H10" s="52">
-        <v>0</v>
-      </c>
-      <c r="I10" s="52">
-        <v>0</v>
-      </c>
-      <c r="J10" s="52">
-        <v>0</v>
-      </c>
-      <c r="K10" s="52">
-        <v>0</v>
-      </c>
-      <c r="L10" s="52">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>0.16463414634146301</v>
       </c>
-      <c r="M10" s="52">
-        <v>0</v>
-      </c>
-      <c r="N10" s="52">
-        <v>0</v>
-      </c>
-      <c r="O10" s="52">
-        <v>0</v>
-      </c>
-      <c r="P10" s="52">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="37">
         <v>10</v>
       </c>
@@ -9204,7 +9409,7 @@
       <c r="C11" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="44">
@@ -9216,38 +9421,38 @@
       <c r="G11" s="10">
         <v>0.53048780487804803</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11">
         <v>0.55487804878048697</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.542682926829268</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11">
         <v>0.70121951219512102</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.77780487804877996</v>
       </c>
-      <c r="L11" s="52">
+      <c r="L11">
         <v>0.70121951219512102</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.82926829268292601</v>
       </c>
-      <c r="N11" s="52">
+      <c r="N11">
         <v>0.81097560975609695</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11">
         <v>0.207317073170731</v>
       </c>
-      <c r="P11" s="52">
+      <c r="P11">
         <v>0.70121951219512102</v>
       </c>
       <c r="Q11" s="20">
         <v>0.48780487804877998</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="37">
         <v>11</v>
       </c>
@@ -9257,7 +9462,7 @@
       <c r="C12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="44">
@@ -9269,38 +9474,38 @@
       <c r="G12" s="10">
         <v>0.542682926829268</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12">
         <v>0.55487804878048697</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.542682926829268</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12">
         <v>0.70121951219512102</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.73780487804878003</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12">
         <v>0.69512195121951204</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.82926829268292601</v>
       </c>
-      <c r="N12" s="52">
+      <c r="N12">
         <v>0.81707317073170704</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12">
         <v>0.74390243902439002</v>
       </c>
-      <c r="P12" s="52">
+      <c r="P12">
         <v>0.71341463414634099</v>
       </c>
       <c r="Q12" s="20">
         <v>0.56707317073170704</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38">
         <v>12</v>
       </c>
@@ -9351,6 +9556,56 @@
       </c>
       <c r="Q13" s="18">
         <v>0.56707317073170704</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <f>MAX(G2:G13)</f>
+        <v>0.57926829268292601</v>
+      </c>
+      <c r="H14">
+        <f t="shared" ref="H14:Q14" si="0">MAX(H2:H13)</f>
+        <v>0.71365853658536504</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0.63487804878048704</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>0.81776585365853605</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>0.77780487804877996</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>0.77180731707316996</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>0.84556829268292599</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="0"/>
+        <v>0.835365853658536</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>0.75609756097560898</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="0"/>
+        <v>0.80887804878048697</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>0.68292682926829196</v>
+      </c>
+      <c r="R14">
+        <f>MAX(G14:Q14)</f>
+        <v>0.84556829268292599</v>
       </c>
     </row>
   </sheetData>
@@ -9359,8 +9614,769 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03780168-3C3F-0548-A539-C4D2A37EEAEE}">
+  <dimension ref="A1:R14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1640625" style="1" customWidth="1"/>
+    <col min="7" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" customWidth="1"/>
+    <col min="13" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" s="36">
+        <v>1</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="43">
+        <v>1</v>
+      </c>
+      <c r="F2" s="23">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0.104</v>
+      </c>
+      <c r="L2" s="7">
+        <v>0.248</v>
+      </c>
+      <c r="M2" s="7">
+        <v>0</v>
+      </c>
+      <c r="N2" s="7">
+        <v>0</v>
+      </c>
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" s="37">
+        <v>2</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="44">
+        <v>1</v>
+      </c>
+      <c r="F3" s="24">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0.114</v>
+      </c>
+      <c r="H3">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="I3">
+        <v>0.308</v>
+      </c>
+      <c r="J3">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="K3">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="L3">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="O3">
+        <v>0.33</v>
+      </c>
+      <c r="P3">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="Q3" s="20">
+        <v>0.314</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A4" s="37">
+        <v>3</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="44">
+        <v>1</v>
+      </c>
+      <c r="F4" s="24">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0.224</v>
+      </c>
+      <c r="H4">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I4">
+        <v>0.308</v>
+      </c>
+      <c r="J4">
+        <v>0.308</v>
+      </c>
+      <c r="K4">
+        <v>0.3</v>
+      </c>
+      <c r="L4">
+        <v>0.312</v>
+      </c>
+      <c r="M4">
+        <v>0.33</v>
+      </c>
+      <c r="N4">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="O4">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="P4">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="Q4" s="20">
+        <v>0.32700000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="38">
+        <v>4</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="45">
+        <v>1</v>
+      </c>
+      <c r="F5" s="25">
+        <v>1</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="H5" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="I5" s="13">
+        <v>0.308</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="K5" s="13">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="L5" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="M5" s="13">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="N5" s="13">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="O5" s="13">
+        <v>0.33</v>
+      </c>
+      <c r="P5" s="13">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="Q5" s="18">
+        <v>0.314</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" s="36">
+        <v>5</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="43">
+        <v>1</v>
+      </c>
+      <c r="F6" s="23">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2E-3</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="37">
+        <v>6</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="44">
+        <v>1</v>
+      </c>
+      <c r="F7" s="24">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="H7">
+        <v>0.224</v>
+      </c>
+      <c r="I7">
+        <v>0.318</v>
+      </c>
+      <c r="J7">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="K7">
+        <v>0.312</v>
+      </c>
+      <c r="L7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M7">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="N7">
+        <v>0.33</v>
+      </c>
+      <c r="O7">
+        <v>1.2E-2</v>
+      </c>
+      <c r="P7">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>0.23799999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="37">
+        <v>7</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="44">
+        <v>1</v>
+      </c>
+      <c r="F8" s="24">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0.314</v>
+      </c>
+      <c r="H8">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="I8">
+        <v>0.316</v>
+      </c>
+      <c r="J8">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="K8">
+        <v>0.32</v>
+      </c>
+      <c r="L8">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="N8">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="O8">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="P8">
+        <v>0.33</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>0.28799999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="38">
+        <v>8</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="45">
+        <v>1</v>
+      </c>
+      <c r="F9" s="25">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="I9" s="13">
+        <v>0.316</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="K9" s="13">
+        <v>0.314</v>
+      </c>
+      <c r="L9" s="13">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M9" s="13">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="N9" s="13">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="O9" s="13">
+        <v>0.32</v>
+      </c>
+      <c r="P9" s="13">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>0.23799999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="36">
+        <v>9</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="43">
+        <v>1</v>
+      </c>
+      <c r="F10" s="23">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <v>1.6E-2</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="37">
+        <v>10</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="44">
+        <v>1</v>
+      </c>
+      <c r="F11" s="24">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0.25</v>
+      </c>
+      <c r="H11">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I11">
+        <v>0.33</v>
+      </c>
+      <c r="J11">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="K11">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="L11">
+        <v>0.318</v>
+      </c>
+      <c r="M11">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="N11">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="O11">
+        <v>0.214</v>
+      </c>
+      <c r="P11">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="Q11" s="20">
+        <v>0.16600000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="37">
+        <v>11</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="44">
+        <v>1</v>
+      </c>
+      <c r="F12" s="24">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="H12">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I12">
+        <v>0.33</v>
+      </c>
+      <c r="J12">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="K12">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="L12">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="M12">
+        <v>0.33</v>
+      </c>
+      <c r="N12">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="O12">
+        <v>0.33</v>
+      </c>
+      <c r="P12">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="Q12" s="20">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="38">
+        <v>12</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="45">
+        <v>1</v>
+      </c>
+      <c r="F13" s="25">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="H13" s="13">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I13" s="13">
+        <v>0.33</v>
+      </c>
+      <c r="J13" s="13">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="K13" s="13">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="L13" s="13">
+        <v>0.32</v>
+      </c>
+      <c r="M13" s="13">
+        <v>0.33</v>
+      </c>
+      <c r="N13" s="13">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0.33</v>
+      </c>
+      <c r="P13" s="13">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <f>MAX(G2:G13)</f>
+        <v>0.314</v>
+      </c>
+      <c r="H14">
+        <f t="shared" ref="H14:Q14" si="0">MAX(H2:H13)</f>
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0.33</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="0"/>
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>0.33</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="0"/>
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="R14">
+        <f>MAX(G14:Q14)</f>
+        <v>0.34599999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7177EE37-76A1-244B-B3C6-89EE825C6972}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -9372,7 +10388,7 @@
     <col min="7" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -9425,7 +10441,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="36">
         <v>1</v>
       </c>
@@ -9478,7 +10494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="37">
         <v>2</v>
       </c>
@@ -9488,7 +10504,7 @@
       <c r="C3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="44">
@@ -9497,41 +10513,41 @@
       <c r="F3" s="24">
         <v>1</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3">
         <v>0.43</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3">
         <v>0.442</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.49</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3">
         <v>0.59399999999999997</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3">
         <v>0.622</v>
       </c>
-      <c r="L3" s="52">
+      <c r="L3">
         <v>0.628</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.73599999999999999</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3">
         <v>0.73399999999999999</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3">
         <v>0.52400000000000002</v>
       </c>
-      <c r="P3" s="52">
+      <c r="P3">
         <v>0.56399999999999995</v>
       </c>
       <c r="Q3" s="20">
         <v>0.54</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="37">
         <v>3</v>
       </c>
@@ -9541,7 +10557,7 @@
       <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="44">
@@ -9550,41 +10566,41 @@
       <c r="F4" s="24">
         <v>1</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4">
         <v>0.42799999999999999</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.49399999999999999</v>
       </c>
-      <c r="J4" s="52">
+      <c r="J4">
         <v>0.59799999999999998</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4">
         <v>0.622</v>
       </c>
-      <c r="L4" s="52">
+      <c r="L4">
         <v>0.65300000000000002</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.73599999999999999</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4">
         <v>0.73399999999999999</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4">
         <v>0.56340000000000001</v>
       </c>
-      <c r="P4" s="52">
+      <c r="P4">
         <v>0.60499999999999998</v>
       </c>
       <c r="Q4" s="20">
         <v>0.54600000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>4</v>
       </c>
@@ -9637,7 +10653,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="36">
         <v>5</v>
       </c>
@@ -9690,7 +10706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="37">
         <v>6</v>
       </c>
@@ -9700,7 +10716,7 @@
       <c r="C7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="44">
@@ -9709,41 +10725,41 @@
       <c r="F7" s="24">
         <v>1</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7">
         <v>0.496</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7">
         <v>0.45400000000000001</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.49199999999999999</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.61799999999999999</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7">
         <v>0.57799999999999996</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.72</v>
       </c>
-      <c r="N7" s="52">
+      <c r="N7">
         <v>0.72799999999999998</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="P7" s="52">
+      <c r="P7">
         <v>0.55000000000000004</v>
       </c>
       <c r="Q7" s="20">
         <v>0.51200000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="37">
         <v>7</v>
       </c>
@@ -9753,7 +10769,7 @@
       <c r="C8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="44">
@@ -9762,41 +10778,41 @@
       <c r="F8" s="24">
         <v>1</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8">
         <v>0.496</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8">
         <v>0.48199999999999998</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.49199999999999999</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.622</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8">
         <v>0.60799999999999998</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.72</v>
       </c>
-      <c r="N8" s="52">
+      <c r="N8">
         <v>0.72799999999999998</v>
       </c>
-      <c r="O8" s="52">
+      <c r="O8">
         <v>0.51</v>
       </c>
-      <c r="P8" s="52">
+      <c r="P8">
         <v>0.56799999999999995</v>
       </c>
       <c r="Q8" s="20">
         <v>0.51400000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="38">
         <v>8</v>
       </c>
@@ -9849,7 +10865,7 @@
         <v>0.51200000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="36">
         <v>9</v>
       </c>
@@ -9902,7 +10918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="37">
         <v>10</v>
       </c>
@@ -9912,7 +10928,7 @@
       <c r="C11" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="44">
@@ -9921,41 +10937,41 @@
       <c r="F11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11">
         <v>0.46</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.498</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11">
         <v>0.54600000000000004</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.60399999999999998</v>
       </c>
-      <c r="L11" s="52">
+      <c r="L11">
         <v>0.61</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.71199999999999997</v>
       </c>
-      <c r="N11" s="52">
+      <c r="N11">
         <v>0.71</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11">
         <v>0.24</v>
       </c>
-      <c r="P11" s="52">
+      <c r="P11">
         <v>0.54800000000000004</v>
       </c>
       <c r="Q11" s="20">
         <v>0.54200000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="37">
         <v>11</v>
       </c>
@@ -9965,7 +10981,7 @@
       <c r="C12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="44">
@@ -9974,41 +10990,41 @@
       <c r="F12" s="24">
         <v>1</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12">
         <v>0.47</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12">
         <v>0.62</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.498</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12">
         <v>0.54600000000000004</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.60399999999999998</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12">
         <v>0.622</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.71199999999999997</v>
       </c>
-      <c r="N12" s="52">
+      <c r="N12">
         <v>0.71</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12">
         <v>0.502</v>
       </c>
-      <c r="P12" s="52">
+      <c r="P12">
         <v>0.54800000000000004</v>
       </c>
       <c r="Q12" s="20">
         <v>0.54200000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38">
         <v>12</v>
       </c>
@@ -10059,6 +11075,56 @@
       </c>
       <c r="Q13" s="18">
         <v>0.54200000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <f>MAX(G2:G13)</f>
+        <v>0.496</v>
+      </c>
+      <c r="H14">
+        <f t="shared" ref="H14:Q14" si="0">MAX(H2:H13)</f>
+        <v>0.62</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>0.73599999999999999</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="0"/>
+        <v>0.749</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>0.56340000000000001</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="0"/>
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="R14">
+        <f>MAX(G14:Q14)</f>
+        <v>0.749</v>
       </c>
     </row>
   </sheetData>
@@ -10067,719 +11133,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03780168-3C3F-0548-A539-C4D2A37EEAEE}">
-  <dimension ref="A1:Q13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1640625" style="1" customWidth="1"/>
-    <col min="7" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" ht="158" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="P1" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q1" s="50" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="36">
-        <v>1</v>
-      </c>
-      <c r="B2" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="43">
-        <v>1</v>
-      </c>
-      <c r="F2" s="23">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0.05</v>
-      </c>
-      <c r="H2" s="7">
-        <v>0</v>
-      </c>
-      <c r="I2" s="7">
-        <v>0</v>
-      </c>
-      <c r="J2" s="7">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0.104</v>
-      </c>
-      <c r="L2" s="7">
-        <v>0.248</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7">
-        <v>0</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="37">
-        <v>2</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="44">
-        <v>1</v>
-      </c>
-      <c r="F3" s="24">
-        <v>1</v>
-      </c>
-      <c r="G3" s="52">
-        <v>0.114</v>
-      </c>
-      <c r="H3" s="52">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="I3" s="52">
-        <v>0.308</v>
-      </c>
-      <c r="J3" s="52">
-        <v>0.29399999999999998</v>
-      </c>
-      <c r="K3" s="52">
-        <v>0.26800000000000002</v>
-      </c>
-      <c r="L3" s="52">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="M3" s="52">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="N3" s="52">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="O3" s="52">
-        <v>0.33</v>
-      </c>
-      <c r="P3" s="52">
-        <v>0.34300000000000003</v>
-      </c>
-      <c r="Q3" s="20">
-        <v>0.314</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="37">
-        <v>3</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="44">
-        <v>1</v>
-      </c>
-      <c r="F4" s="24">
-        <v>1</v>
-      </c>
-      <c r="G4" s="52">
-        <v>0.224</v>
-      </c>
-      <c r="H4" s="52">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="I4" s="52">
-        <v>0.308</v>
-      </c>
-      <c r="J4" s="52">
-        <v>0.308</v>
-      </c>
-      <c r="K4" s="52">
-        <v>0.3</v>
-      </c>
-      <c r="L4" s="52">
-        <v>0.312</v>
-      </c>
-      <c r="M4" s="52">
-        <v>0.33</v>
-      </c>
-      <c r="N4" s="52">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="O4" s="52">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="P4" s="52">
-        <v>0.33200000000000002</v>
-      </c>
-      <c r="Q4" s="20">
-        <v>0.32700000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38">
-        <v>4</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="45">
-        <v>1</v>
-      </c>
-      <c r="F5" s="25">
-        <v>1</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0.15</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0.27</v>
-      </c>
-      <c r="I5" s="13">
-        <v>0.308</v>
-      </c>
-      <c r="J5" s="13">
-        <v>0.28399999999999997</v>
-      </c>
-      <c r="K5" s="13">
-        <v>0.26800000000000002</v>
-      </c>
-      <c r="L5" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="M5" s="13">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="N5" s="13">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="O5" s="13">
-        <v>0.33</v>
-      </c>
-      <c r="P5" s="13">
-        <v>0.33200000000000002</v>
-      </c>
-      <c r="Q5" s="18">
-        <v>0.314</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
-        <v>5</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="43">
-        <v>1</v>
-      </c>
-      <c r="F6" s="23">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
-        <v>2E-3</v>
-      </c>
-      <c r="H6" s="7">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="37">
-        <v>6</v>
-      </c>
-      <c r="B7" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="44">
-        <v>1</v>
-      </c>
-      <c r="F7" s="24">
-        <v>1</v>
-      </c>
-      <c r="G7" s="52">
-        <v>0.30399999999999999</v>
-      </c>
-      <c r="H7" s="52">
-        <v>0.224</v>
-      </c>
-      <c r="I7" s="52">
-        <v>0.318</v>
-      </c>
-      <c r="J7" s="52">
-        <v>0.27600000000000002</v>
-      </c>
-      <c r="K7" s="52">
-        <v>0.312</v>
-      </c>
-      <c r="L7" s="52">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M7" s="52">
-        <v>0.33200000000000002</v>
-      </c>
-      <c r="N7" s="52">
-        <v>0.33</v>
-      </c>
-      <c r="O7" s="52">
-        <v>1.2E-2</v>
-      </c>
-      <c r="P7" s="52">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="Q7" s="20">
-        <v>0.23799999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="37">
-        <v>7</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="52" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="44">
-        <v>1</v>
-      </c>
-      <c r="F8" s="24">
-        <v>1</v>
-      </c>
-      <c r="G8" s="52">
-        <v>0.314</v>
-      </c>
-      <c r="H8" s="52">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="I8" s="52">
-        <v>0.316</v>
-      </c>
-      <c r="J8" s="52">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="K8" s="52">
-        <v>0.32</v>
-      </c>
-      <c r="L8" s="52">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="M8" s="52">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="N8" s="52">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="O8" s="52">
-        <v>0.32400000000000001</v>
-      </c>
-      <c r="P8" s="52">
-        <v>0.33</v>
-      </c>
-      <c r="Q8" s="20">
-        <v>0.28799999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38">
-        <v>8</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="45">
-        <v>1</v>
-      </c>
-      <c r="F9" s="25">
-        <v>1</v>
-      </c>
-      <c r="G9" s="13">
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="H9" s="13">
-        <v>0.23400000000000001</v>
-      </c>
-      <c r="I9" s="13">
-        <v>0.316</v>
-      </c>
-      <c r="J9" s="13">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="K9" s="13">
-        <v>0.314</v>
-      </c>
-      <c r="L9" s="13">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M9" s="13">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="N9" s="13">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="O9" s="13">
-        <v>0.32</v>
-      </c>
-      <c r="P9" s="13">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>0.23799999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="36">
-        <v>9</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="43">
-        <v>1</v>
-      </c>
-      <c r="F10" s="23">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H10" s="7">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7">
-        <v>0</v>
-      </c>
-      <c r="J10" s="7">
-        <v>0</v>
-      </c>
-      <c r="K10" s="7">
-        <v>0</v>
-      </c>
-      <c r="L10" s="7">
-        <v>1.6E-2</v>
-      </c>
-      <c r="M10" s="7">
-        <v>0</v>
-      </c>
-      <c r="N10" s="7">
-        <v>0</v>
-      </c>
-      <c r="O10" s="7">
-        <v>0</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="37">
-        <v>10</v>
-      </c>
-      <c r="B11" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="44">
-        <v>1</v>
-      </c>
-      <c r="F11" s="24">
-        <v>1</v>
-      </c>
-      <c r="G11" s="52">
-        <v>0.25</v>
-      </c>
-      <c r="H11" s="52">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="I11" s="52">
-        <v>0.33</v>
-      </c>
-      <c r="J11" s="52">
-        <v>0.34599999999999997</v>
-      </c>
-      <c r="K11" s="52">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="L11" s="52">
-        <v>0.318</v>
-      </c>
-      <c r="M11" s="52">
-        <v>0.33900000000000002</v>
-      </c>
-      <c r="N11" s="52">
-        <v>0.33400000000000002</v>
-      </c>
-      <c r="O11" s="52">
-        <v>0.214</v>
-      </c>
-      <c r="P11" s="52">
-        <v>0.34300000000000003</v>
-      </c>
-      <c r="Q11" s="20">
-        <v>0.16600000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="37">
-        <v>11</v>
-      </c>
-      <c r="B12" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="52" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="44">
-        <v>1</v>
-      </c>
-      <c r="F12" s="24">
-        <v>1</v>
-      </c>
-      <c r="G12" s="52">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="H12" s="52">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="I12" s="52">
-        <v>0.33</v>
-      </c>
-      <c r="J12" s="52">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="K12" s="52">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="L12" s="52">
-        <v>0.34399999999999997</v>
-      </c>
-      <c r="M12" s="52">
-        <v>0.33</v>
-      </c>
-      <c r="N12" s="52">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="O12" s="52">
-        <v>0.33</v>
-      </c>
-      <c r="P12" s="52">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="Q12" s="20">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38">
-        <v>12</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="45">
-        <v>1</v>
-      </c>
-      <c r="F13" s="25">
-        <v>1</v>
-      </c>
-      <c r="G13" s="13">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="H13" s="13">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="I13" s="13">
-        <v>0.33</v>
-      </c>
-      <c r="J13" s="13">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="K13" s="13">
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="L13" s="13">
-        <v>0.32</v>
-      </c>
-      <c r="M13" s="13">
-        <v>0.33</v>
-      </c>
-      <c r="N13" s="13">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="O13" s="13">
-        <v>0.33</v>
-      </c>
-      <c r="P13" s="13">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="Q13" s="18">
-        <v>0.18</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2445879-30D3-F047-B1C3-AB54499E3CB9}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -10791,7 +11147,7 @@
     <col min="7" max="17" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -10844,7 +11200,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="36">
         <v>1</v>
       </c>
@@ -10897,7 +11253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37">
         <v>2</v>
       </c>
@@ -10907,7 +11263,7 @@
       <c r="C3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="44">
@@ -10916,13 +11272,13 @@
       <c r="F3" s="24">
         <v>1</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3">
         <v>0.141975308641975</v>
       </c>
       <c r="H3" s="2">
         <v>0.25925925925925902</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.172839506172839</v>
       </c>
       <c r="J3" s="2">
@@ -10934,13 +11290,13 @@
       <c r="L3" s="2">
         <v>0.29012345679012302</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.22839506172839499</v>
       </c>
       <c r="N3" s="2">
         <v>0.22839506172839499</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3">
         <v>0.27160493827160398</v>
       </c>
       <c r="P3" s="2">
@@ -10950,7 +11306,7 @@
         <v>0.25925925925925902</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37">
         <v>3</v>
       </c>
@@ -10960,7 +11316,7 @@
       <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="44">
@@ -10969,13 +11325,13 @@
       <c r="F4" s="24">
         <v>1</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4">
         <v>0.141975308641975</v>
       </c>
       <c r="H4" s="2">
         <v>0.24691358024691301</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.16666666666666599</v>
       </c>
       <c r="J4" s="2">
@@ -10987,13 +11343,13 @@
       <c r="L4" s="2">
         <v>0.28395061728394999</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.22839506172839499</v>
       </c>
       <c r="N4" s="2">
         <v>0.22839506172839499</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4">
         <v>0.22222222222222199</v>
       </c>
       <c r="P4" s="2">
@@ -11003,7 +11359,7 @@
         <v>0.25308641975308599</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>4</v>
       </c>
@@ -11056,7 +11412,7 @@
         <v>0.27525925925925898</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="36">
         <v>5</v>
       </c>
@@ -11109,7 +11465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="37">
         <v>6</v>
       </c>
@@ -11119,7 +11475,7 @@
       <c r="C7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="44">
@@ -11128,31 +11484,31 @@
       <c r="F7" s="24">
         <v>1</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7">
         <v>0.18518518518518501</v>
       </c>
       <c r="H7" s="2">
         <v>0.27160493827160398</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.12345679012345601</v>
       </c>
       <c r="J7" s="2">
         <v>0.22839506172839499</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.27160493827160398</v>
       </c>
       <c r="L7" s="2">
         <v>0.265432098765432</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.24074074074074001</v>
       </c>
       <c r="N7" s="2">
         <v>0.234567901234567</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7">
         <v>9.2592592592592504E-2</v>
       </c>
       <c r="P7" s="2">
@@ -11162,7 +11518,7 @@
         <v>0.234567901234567</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="37">
         <v>7</v>
       </c>
@@ -11172,7 +11528,7 @@
       <c r="C8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="44">
@@ -11181,31 +11537,31 @@
       <c r="F8" s="24">
         <v>1</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8">
         <v>0.18518518518518501</v>
       </c>
       <c r="H8" s="2">
         <v>0.234567901234567</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.13580246913580199</v>
       </c>
       <c r="J8" s="2">
         <v>0.22839506172839499</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.265432098765432</v>
       </c>
       <c r="L8" s="2">
         <v>0.265432098765432</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.24074074074074001</v>
       </c>
       <c r="N8" s="2">
         <v>0.27456790123456698</v>
       </c>
-      <c r="O8" s="52">
+      <c r="O8">
         <v>0.16666666666666599</v>
       </c>
       <c r="P8" s="2">
@@ -11215,7 +11571,7 @@
         <v>0.22839506172839499</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="38">
         <v>8</v>
       </c>
@@ -11268,7 +11624,7 @@
         <v>0.24074074074074001</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="36">
         <v>9</v>
       </c>
@@ -11321,7 +11677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="37">
         <v>10</v>
       </c>
@@ -11331,7 +11687,7 @@
       <c r="C11" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="44">
@@ -11340,31 +11696,31 @@
       <c r="F11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11">
         <v>0.148148148148148</v>
       </c>
       <c r="H11" s="2">
         <v>0.24074074074074001</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.16666666666666599</v>
       </c>
       <c r="J11" s="2">
         <v>0.21604938271604901</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.25308641975308599</v>
       </c>
       <c r="L11" s="2">
         <v>0.27160493827160398</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.22839506172839499</v>
       </c>
       <c r="N11" s="2">
         <v>0.19753086419752999</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11">
         <v>0.16049382716049301</v>
       </c>
       <c r="P11" s="2">
@@ -11374,7 +11730,7 @@
         <v>0.22839506172839499</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="37">
         <v>11</v>
       </c>
@@ -11384,7 +11740,7 @@
       <c r="C12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="44">
@@ -11393,31 +11749,31 @@
       <c r="F12" s="24">
         <v>1</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12">
         <v>0.15432098765432001</v>
       </c>
       <c r="H12" s="2">
         <v>0.24074074074074001</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.203703703703703</v>
       </c>
       <c r="J12" s="2">
         <v>0.22222222222222199</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.25308641975308599</v>
       </c>
       <c r="L12" s="2">
         <v>0.27160493827160398</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.28291358024691299</v>
       </c>
       <c r="N12" s="2">
         <v>0.234567901234567</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12">
         <v>0.19753086419752999</v>
       </c>
       <c r="P12" s="2">
@@ -11427,7 +11783,7 @@
         <v>0.22839506172839499</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38">
         <v>12</v>
       </c>
@@ -11478,6 +11834,56 @@
       </c>
       <c r="Q13" s="18">
         <v>0.22839506172839499</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <f>MAX(G2:G13)</f>
+        <v>0.21247565469999999</v>
+      </c>
+      <c r="H14">
+        <f t="shared" ref="H14:Q14" si="0">MAX(H2:H13)</f>
+        <v>0.29395061728395</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0.21970370370370301</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>0.26925925925925898</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>0.31522345679012298</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>0.307523456790123</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>0.28291358024691299</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="0"/>
+        <v>0.27956790123456698</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>0.27160493827160398</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="0"/>
+        <v>0.30996913580246899</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>0.27525925925925898</v>
+      </c>
+      <c r="R14">
+        <f>MAX(G14:Q14)</f>
+        <v>0.31522345679012298</v>
       </c>
     </row>
   </sheetData>
@@ -11611,25 +12017,25 @@
       <c r="F3" s="24">
         <v>1</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3">
         <v>0.172839506172839</v>
       </c>
       <c r="H3" s="2">
         <v>7.4074074074074001E-2</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3">
         <v>0.296296296296296</v>
       </c>
       <c r="J3" s="2">
         <v>0.18518518518518501</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3">
         <v>0.234567901234567</v>
       </c>
       <c r="L3" s="2">
         <v>0.30864197530864101</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3">
         <v>0.296296296296296</v>
       </c>
       <c r="N3" s="2">
@@ -11658,25 +12064,25 @@
       <c r="F4" s="24">
         <v>1</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4">
         <v>0.16666666666666599</v>
       </c>
       <c r="H4" s="2">
         <v>0.117283950617283</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4">
         <v>0.28395061728394999</v>
       </c>
       <c r="J4" s="2">
         <v>0.18518518518518501</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4">
         <v>0.234567901234567</v>
       </c>
       <c r="L4" s="2">
         <v>0.30864197530864101</v>
       </c>
-      <c r="M4" s="52">
+      <c r="M4">
         <v>0.29012345679012302</v>
       </c>
       <c r="N4" s="2">
@@ -11752,25 +12158,25 @@
       <c r="F6" s="24">
         <v>1</v>
       </c>
-      <c r="G6" s="52">
+      <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6">
         <v>0</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
       </c>
-      <c r="K6" s="52">
+      <c r="K6">
         <v>0</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
       </c>
-      <c r="M6" s="52">
+      <c r="M6">
         <v>0</v>
       </c>
       <c r="N6" s="2">
@@ -11799,25 +12205,25 @@
       <c r="F7" s="24">
         <v>1</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7">
         <v>0.16666666666666599</v>
       </c>
       <c r="H7" s="2">
         <v>7.4074074074074001E-2</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7">
         <v>0.22839506172839499</v>
       </c>
       <c r="J7" s="2">
         <v>0.16049382716049301</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7">
         <v>0.22222222222222199</v>
       </c>
       <c r="L7" s="2">
         <v>0.265432098765432</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7">
         <v>0.27160493827160398</v>
       </c>
       <c r="N7" s="2">
@@ -11846,25 +12252,25 @@
       <c r="F8" s="24">
         <v>1</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8">
         <v>0.16666666666666599</v>
       </c>
       <c r="H8" s="2">
         <v>9.8765432098765399E-2</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8">
         <v>0.18518518518518501</v>
       </c>
       <c r="J8" s="2">
         <v>0.203703703703703</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8">
         <v>0.22839506172839499</v>
       </c>
       <c r="L8" s="2">
         <v>0.25308641975308599</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8">
         <v>0.28395061728394999</v>
       </c>
       <c r="N8" s="2">
@@ -11893,25 +12299,25 @@
       <c r="F9" s="24">
         <v>1</v>
       </c>
-      <c r="G9" s="52">
+      <c r="G9">
         <v>0.16666666666666599</v>
       </c>
       <c r="H9" s="2">
         <v>9.8765432098765399E-2</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9">
         <v>0.22839506172839499</v>
       </c>
       <c r="J9" s="2">
         <v>0.203703703703703</v>
       </c>
-      <c r="K9" s="52">
+      <c r="K9">
         <v>0.22839506172839499</v>
       </c>
       <c r="L9" s="2">
         <v>0.265432098765432</v>
       </c>
-      <c r="M9" s="52">
+      <c r="M9">
         <v>0.27160493827160398</v>
       </c>
       <c r="N9" s="2">
@@ -11987,25 +12393,25 @@
       <c r="F11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11">
         <v>0.148148148148148</v>
       </c>
       <c r="H11" s="2">
         <v>5.5555555555555497E-2</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11">
         <v>0.21604938271604901</v>
       </c>
       <c r="J11" s="2">
         <v>0.172839506172839</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11">
         <v>0.22839506172839499</v>
       </c>
       <c r="L11" s="2">
         <v>0.25925925925925902</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11">
         <v>0.27777777777777701</v>
       </c>
       <c r="N11" s="2">
@@ -12034,25 +12440,25 @@
       <c r="F12" s="24">
         <v>1</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12">
         <v>0.148148148148148</v>
       </c>
       <c r="H12" s="2">
         <v>9.8765432098765399E-2</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12">
         <v>0.25925925925925902</v>
       </c>
       <c r="J12" s="2">
         <v>0.22222222222222199</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12">
         <v>0.234567901234567</v>
       </c>
       <c r="L12" s="2">
         <v>0.25925925925925902</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12">
         <v>0.265432098765432</v>
       </c>
       <c r="N12" s="2">
